--- a/test/Extract Thermo-calc Results-Melting Range/Al-Cu-Si_COST/melting_range.xlsx
+++ b/test/Extract Thermo-calc Results-Melting Range/Al-Cu-Si_COST/melting_range.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
   <si>
     <t>File</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>Al0.005Cu0.100Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Cu0.00Si_np-T.exp</t>
   </si>
   <si>
     <t>Al0.010Cu0.000Si_np-T.exp</t>
@@ -1709,7 +1712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F441"/>
+  <dimension ref="A1:F442"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2557,19 +2560,19 @@
         <v>47</v>
       </c>
       <c r="B43">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>930.86792784</v>
+        <v>933.46167474</v>
       </c>
       <c r="E43">
-        <v>907.39262524</v>
+        <v>933.38564453</v>
       </c>
       <c r="F43">
-        <v>23.47530259999996</v>
+        <v>0.07603020999999899</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2580,16 +2583,16 @@
         <v>0.01</v>
       </c>
       <c r="C44">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>927.92125844</v>
+        <v>930.86792784</v>
       </c>
       <c r="E44">
-        <v>879.8709763099999</v>
+        <v>907.39262524</v>
       </c>
       <c r="F44">
-        <v>48.05028213000003</v>
+        <v>23.47530259999996</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2600,16 +2603,16 @@
         <v>0.01</v>
       </c>
       <c r="C45">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D45">
-        <v>924.94690386</v>
+        <v>927.92125844</v>
       </c>
       <c r="E45">
-        <v>854.10694616</v>
+        <v>879.8709763099999</v>
       </c>
       <c r="F45">
-        <v>70.83995770000001</v>
+        <v>48.05028213000003</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2620,16 +2623,16 @@
         <v>0.01</v>
       </c>
       <c r="C46">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D46">
-        <v>921.94368497</v>
+        <v>924.94690386</v>
       </c>
       <c r="E46">
-        <v>834.49758259</v>
+        <v>854.10694616</v>
       </c>
       <c r="F46">
-        <v>87.44610238000007</v>
+        <v>70.83995770000001</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2640,16 +2643,16 @@
         <v>0.01</v>
       </c>
       <c r="C47">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D47">
-        <v>918.91046819</v>
+        <v>921.94368497</v>
       </c>
       <c r="E47">
-        <v>834.41906471</v>
+        <v>834.49758259</v>
       </c>
       <c r="F47">
-        <v>84.49140347999992</v>
+        <v>87.44610238000007</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2660,16 +2663,16 @@
         <v>0.01</v>
       </c>
       <c r="C48">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D48">
-        <v>915.84616377</v>
+        <v>918.91046819</v>
       </c>
       <c r="E48">
-        <v>834.33976039</v>
+        <v>834.41906471</v>
       </c>
       <c r="F48">
-        <v>81.50640337999994</v>
+        <v>84.49140347999992</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2680,16 +2683,16 @@
         <v>0.01</v>
       </c>
       <c r="C49">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D49">
-        <v>912.74972593</v>
+        <v>915.84616377</v>
       </c>
       <c r="E49">
-        <v>834.25965823</v>
+        <v>834.33976039</v>
       </c>
       <c r="F49">
-        <v>78.49006769999994</v>
+        <v>81.50640337999994</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2700,16 +2703,16 @@
         <v>0.01</v>
       </c>
       <c r="C50">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D50">
-        <v>909.62015246</v>
+        <v>912.74972593</v>
       </c>
       <c r="E50">
-        <v>834.17874621</v>
+        <v>834.25965823</v>
       </c>
       <c r="F50">
-        <v>75.44140625</v>
+        <v>78.49006769999994</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2720,16 +2723,16 @@
         <v>0.01</v>
       </c>
       <c r="C51">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D51">
-        <v>906.45648366</v>
+        <v>909.62015246</v>
       </c>
       <c r="E51">
-        <v>834.0970121300001</v>
+        <v>834.17874621</v>
       </c>
       <c r="F51">
-        <v>72.35947152999995</v>
+        <v>75.44140625</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2740,16 +2743,16 @@
         <v>0.01</v>
       </c>
       <c r="C52">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D52">
-        <v>903.2578056</v>
+        <v>906.45648366</v>
       </c>
       <c r="E52">
-        <v>834.01444344</v>
+        <v>834.0970121300001</v>
       </c>
       <c r="F52">
-        <v>69.24336215999995</v>
+        <v>72.35947152999995</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2760,16 +2763,16 @@
         <v>0.01</v>
       </c>
       <c r="C53">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D53">
-        <v>900.02324245</v>
+        <v>903.2578056</v>
       </c>
       <c r="E53">
-        <v>833.9310273999999</v>
+        <v>834.01444344</v>
       </c>
       <c r="F53">
-        <v>66.09221505000005</v>
+        <v>69.24336215999995</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2780,16 +2783,16 @@
         <v>0.01</v>
       </c>
       <c r="C54">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D54">
-        <v>896.75196336</v>
+        <v>900.02324245</v>
       </c>
       <c r="E54">
-        <v>833.8467511</v>
+        <v>833.9310273999999</v>
       </c>
       <c r="F54">
-        <v>62.90521225999998</v>
+        <v>66.09221505000005</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2800,16 +2803,16 @@
         <v>0.01</v>
       </c>
       <c r="C55">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D55">
-        <v>893.44317875</v>
+        <v>896.75196336</v>
       </c>
       <c r="E55">
-        <v>833.76160121</v>
+        <v>833.8467511</v>
       </c>
       <c r="F55">
-        <v>59.68157754000003</v>
+        <v>62.90521225999998</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2820,16 +2823,16 @@
         <v>0.01</v>
       </c>
       <c r="C56">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D56">
-        <v>890.09614042</v>
+        <v>893.44317875</v>
       </c>
       <c r="E56">
-        <v>833.6755642000001</v>
+        <v>833.76160121</v>
       </c>
       <c r="F56">
-        <v>56.42057621999993</v>
+        <v>59.68157754000003</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2840,16 +2843,16 @@
         <v>0.01</v>
       </c>
       <c r="C57">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D57">
-        <v>886.71014127</v>
+        <v>890.09614042</v>
       </c>
       <c r="E57">
-        <v>833.58862628</v>
+        <v>833.6755642000001</v>
       </c>
       <c r="F57">
-        <v>53.12151499000004</v>
+        <v>56.42057621999993</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2860,16 +2863,16 @@
         <v>0.01</v>
       </c>
       <c r="C58">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D58">
-        <v>883.28451518</v>
+        <v>886.71014127</v>
       </c>
       <c r="E58">
-        <v>833.50077333</v>
+        <v>833.58862628</v>
       </c>
       <c r="F58">
-        <v>49.78374184999996</v>
+        <v>53.12151499000004</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2880,16 +2883,16 @@
         <v>0.01</v>
       </c>
       <c r="C59">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D59">
-        <v>879.81863646</v>
+        <v>883.28451518</v>
       </c>
       <c r="E59">
-        <v>833.41199098</v>
+        <v>833.50077333</v>
       </c>
       <c r="F59">
-        <v>46.40664547999995</v>
+        <v>49.78374184999996</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2900,16 +2903,16 @@
         <v>0.01</v>
       </c>
       <c r="C60">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D60">
-        <v>876.31191967</v>
+        <v>879.81863646</v>
       </c>
       <c r="E60">
-        <v>833.32226453</v>
+        <v>833.41199098</v>
       </c>
       <c r="F60">
-        <v>42.98965513999997</v>
+        <v>46.40664547999995</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2920,16 +2923,16 @@
         <v>0.01</v>
       </c>
       <c r="C61">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D61">
-        <v>872.7638193</v>
+        <v>876.31191967</v>
       </c>
       <c r="E61">
-        <v>833.23157899</v>
+        <v>833.32226453</v>
       </c>
       <c r="F61">
-        <v>39.53224031000002</v>
+        <v>42.98965513999997</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2940,16 +2943,16 @@
         <v>0.01</v>
       </c>
       <c r="C62">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D62">
-        <v>869.17382944</v>
+        <v>872.7638193</v>
       </c>
       <c r="E62">
-        <v>833.13991905</v>
+        <v>833.23157899</v>
       </c>
       <c r="F62">
-        <v>36.03391038999996</v>
+        <v>39.53224031000002</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2960,16 +2963,16 @@
         <v>0.01</v>
       </c>
       <c r="C63">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D63">
-        <v>865.5414835300001</v>
+        <v>869.17382944</v>
       </c>
       <c r="E63">
-        <v>833.04726906</v>
+        <v>833.13991905</v>
       </c>
       <c r="F63">
-        <v>32.49421447000009</v>
+        <v>36.03391038999996</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2977,19 +2980,19 @@
         <v>68</v>
       </c>
       <c r="B64">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D64">
-        <v>929.56115245</v>
+        <v>865.5414835300001</v>
       </c>
       <c r="E64">
-        <v>895.12520621</v>
+        <v>833.04726906</v>
       </c>
       <c r="F64">
-        <v>34.43594624000002</v>
+        <v>32.49421447000009</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3000,16 +3003,16 @@
         <v>0.015</v>
       </c>
       <c r="C65">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>926.60701351</v>
+        <v>929.56115245</v>
       </c>
       <c r="E65">
-        <v>868.00924672</v>
+        <v>895.12520621</v>
       </c>
       <c r="F65">
-        <v>58.59776679000004</v>
+        <v>34.43594624000002</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3020,16 +3023,16 @@
         <v>0.015</v>
       </c>
       <c r="C66">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D66">
-        <v>923.62432588</v>
+        <v>926.60701351</v>
       </c>
       <c r="E66">
-        <v>842.894814</v>
+        <v>868.00924672</v>
       </c>
       <c r="F66">
-        <v>80.72951188000002</v>
+        <v>58.59776679000004</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -3040,16 +3043,16 @@
         <v>0.015</v>
       </c>
       <c r="C67">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D67">
-        <v>920.61191673</v>
+        <v>923.62432588</v>
       </c>
       <c r="E67">
-        <v>826.90582384</v>
+        <v>842.894814</v>
       </c>
       <c r="F67">
-        <v>93.70609288999992</v>
+        <v>80.72951188000002</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3060,16 +3063,16 @@
         <v>0.015</v>
       </c>
       <c r="C68">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D68">
-        <v>917.56865822</v>
+        <v>920.61191673</v>
       </c>
       <c r="E68">
-        <v>826.7914501400001</v>
+        <v>826.90582384</v>
       </c>
       <c r="F68">
-        <v>90.77720807999992</v>
+        <v>93.70609288999992</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -3080,16 +3083,16 @@
         <v>0.015</v>
       </c>
       <c r="C69">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D69">
-        <v>914.49346755</v>
+        <v>917.56865822</v>
       </c>
       <c r="E69">
-        <v>826.67596578</v>
+        <v>826.7914501400001</v>
       </c>
       <c r="F69">
-        <v>87.81750177000004</v>
+        <v>90.77720807999992</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3100,16 +3103,16 @@
         <v>0.015</v>
       </c>
       <c r="C70">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D70">
-        <v>911.38530615</v>
+        <v>914.49346755</v>
       </c>
       <c r="E70">
-        <v>826.55935496</v>
+        <v>826.67596578</v>
       </c>
       <c r="F70">
-        <v>84.82595119000007</v>
+        <v>87.81750177000004</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3120,16 +3123,16 @@
         <v>0.015</v>
       </c>
       <c r="C71">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D71">
-        <v>908.2431794</v>
+        <v>911.38530615</v>
       </c>
       <c r="E71">
-        <v>826.44160141</v>
+        <v>826.55935496</v>
       </c>
       <c r="F71">
-        <v>81.80157799000006</v>
+        <v>84.82595119000007</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3140,16 +3143,16 @@
         <v>0.015</v>
       </c>
       <c r="C72">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D72">
-        <v>905.0661370399999</v>
+        <v>908.2431794</v>
       </c>
       <c r="E72">
-        <v>826.3226887</v>
+        <v>826.44160141</v>
       </c>
       <c r="F72">
-        <v>78.74344833999999</v>
+        <v>81.80157799000006</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3160,16 +3163,16 @@
         <v>0.015</v>
       </c>
       <c r="C73">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D73">
-        <v>901.85326964</v>
+        <v>905.0661370399999</v>
       </c>
       <c r="E73">
-        <v>826.20259981</v>
+        <v>826.3226887</v>
       </c>
       <c r="F73">
-        <v>75.65066982999997</v>
+        <v>78.74344833999999</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3180,16 +3183,16 @@
         <v>0.015</v>
       </c>
       <c r="C74">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D74">
-        <v>898.60371418</v>
+        <v>901.85326964</v>
       </c>
       <c r="E74">
-        <v>826.0813178</v>
+        <v>826.20259981</v>
       </c>
       <c r="F74">
-        <v>72.52239638000003</v>
+        <v>75.65066982999997</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3200,16 +3203,16 @@
         <v>0.015</v>
       </c>
       <c r="C75">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D75">
-        <v>895.31664791</v>
+        <v>898.60371418</v>
       </c>
       <c r="E75">
-        <v>825.9588252</v>
+        <v>826.0813178</v>
       </c>
       <c r="F75">
-        <v>69.35782271000005</v>
+        <v>72.52239638000003</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3220,16 +3223,16 @@
         <v>0.015</v>
       </c>
       <c r="C76">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D76">
-        <v>891.99129085</v>
+        <v>895.31664791</v>
       </c>
       <c r="E76">
-        <v>825.8351040700001</v>
+        <v>825.9588252</v>
       </c>
       <c r="F76">
-        <v>66.15618677999998</v>
+        <v>69.35782271000005</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3240,16 +3243,16 @@
         <v>0.015</v>
       </c>
       <c r="C77">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D77">
-        <v>888.6269048299999</v>
+        <v>891.99129085</v>
       </c>
       <c r="E77">
-        <v>825.71013629</v>
+        <v>825.8351040700001</v>
       </c>
       <c r="F77">
-        <v>62.91676853999991</v>
+        <v>66.15618677999998</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3260,16 +3263,16 @@
         <v>0.015</v>
       </c>
       <c r="C78">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D78">
-        <v>885.2227933299999</v>
+        <v>888.6269048299999</v>
       </c>
       <c r="E78">
-        <v>825.58390357</v>
+        <v>825.71013629</v>
       </c>
       <c r="F78">
-        <v>59.63888975999998</v>
+        <v>62.91676853999991</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3280,16 +3283,16 @@
         <v>0.015</v>
       </c>
       <c r="C79">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D79">
-        <v>881.77830096</v>
+        <v>885.2227933299999</v>
       </c>
       <c r="E79">
-        <v>825.4563868499999</v>
+        <v>825.58390357</v>
       </c>
       <c r="F79">
-        <v>56.32191411000008</v>
+        <v>59.63888975999998</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3300,16 +3303,16 @@
         <v>0.015</v>
       </c>
       <c r="C80">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D80">
-        <v>878.29281323</v>
+        <v>881.77830096</v>
       </c>
       <c r="E80">
-        <v>825.32756699</v>
+        <v>825.4563868499999</v>
       </c>
       <c r="F80">
-        <v>52.96524623999994</v>
+        <v>56.32191411000008</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3320,16 +3323,16 @@
         <v>0.015</v>
       </c>
       <c r="C81">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D81">
-        <v>874.76575629</v>
+        <v>878.29281323</v>
       </c>
       <c r="E81">
-        <v>825.1974244</v>
+        <v>825.32756699</v>
       </c>
       <c r="F81">
-        <v>49.56833188999997</v>
+        <v>52.96524623999994</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3340,16 +3343,16 @@
         <v>0.015</v>
       </c>
       <c r="C82">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D82">
-        <v>871.1965965000001</v>
+        <v>874.76575629</v>
       </c>
       <c r="E82">
-        <v>825.06593917</v>
+        <v>825.1974244</v>
       </c>
       <c r="F82">
-        <v>46.13065733000008</v>
+        <v>49.56833188999997</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3360,16 +3363,16 @@
         <v>0.015</v>
       </c>
       <c r="C83">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D83">
-        <v>867.5848402300001</v>
+        <v>871.1965965000001</v>
       </c>
       <c r="E83">
-        <v>824.93309089</v>
+        <v>825.06593917</v>
       </c>
       <c r="F83">
-        <v>42.65174934000004</v>
+        <v>46.13065733000008</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3380,16 +3383,16 @@
         <v>0.015</v>
       </c>
       <c r="C84">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D84">
-        <v>863.93003357</v>
+        <v>867.5848402300001</v>
       </c>
       <c r="E84">
-        <v>824.79885877</v>
+        <v>824.93309089</v>
       </c>
       <c r="F84">
-        <v>39.13117479999994</v>
+        <v>42.65174934000004</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3397,19 +3400,19 @@
         <v>89</v>
       </c>
       <c r="B85">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D85">
-        <v>928.25030607</v>
+        <v>863.93003357</v>
       </c>
       <c r="E85">
-        <v>883.5075303900001</v>
+        <v>824.79885877</v>
       </c>
       <c r="F85">
-        <v>44.74277567999991</v>
+        <v>39.13117479999994</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3420,16 +3423,16 @@
         <v>0.02</v>
       </c>
       <c r="C86">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>925.28853271</v>
+        <v>928.25030607</v>
       </c>
       <c r="E86">
-        <v>856.81396331</v>
+        <v>883.5075303900001</v>
       </c>
       <c r="F86">
-        <v>68.47456940000006</v>
+        <v>44.74277567999991</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3440,16 +3443,16 @@
         <v>0.02</v>
       </c>
       <c r="C87">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D87">
-        <v>922.29733183</v>
+        <v>925.28853271</v>
       </c>
       <c r="E87">
-        <v>832.3493713399999</v>
+        <v>856.81396331</v>
       </c>
       <c r="F87">
-        <v>89.94796049000001</v>
+        <v>68.47456940000006</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3460,16 +3463,16 @@
         <v>0.02</v>
       </c>
       <c r="C88">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D88">
-        <v>919.27553874</v>
+        <v>922.29733183</v>
       </c>
       <c r="E88">
-        <v>819.57491802</v>
+        <v>832.3493713399999</v>
       </c>
       <c r="F88">
-        <v>99.70062071999996</v>
+        <v>89.94796049000001</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3480,16 +3483,16 @@
         <v>0.02</v>
       </c>
       <c r="C89">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D89">
-        <v>916.2220292</v>
+        <v>919.27553874</v>
       </c>
       <c r="E89">
-        <v>819.42856074</v>
+        <v>819.57491802</v>
       </c>
       <c r="F89">
-        <v>96.79346845999999</v>
+        <v>99.70062071999996</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3500,16 +3503,16 @@
         <v>0.02</v>
       </c>
       <c r="C90">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D90">
-        <v>913.13573007</v>
+        <v>916.2220292</v>
       </c>
       <c r="E90">
-        <v>819.28084502</v>
+        <v>819.42856074</v>
       </c>
       <c r="F90">
-        <v>93.85488505000001</v>
+        <v>96.79346845999999</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3520,16 +3523,16 @@
         <v>0.02</v>
       </c>
       <c r="C91">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D91">
-        <v>910.0156084499999</v>
+        <v>913.13573007</v>
       </c>
       <c r="E91">
-        <v>819.13175314</v>
+        <v>819.28084502</v>
       </c>
       <c r="F91">
-        <v>90.88385530999994</v>
+        <v>93.85488505000001</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3540,16 +3543,16 @@
         <v>0.02</v>
       </c>
       <c r="C92">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D92">
-        <v>906.86067902</v>
+        <v>910.0156084499999</v>
       </c>
       <c r="E92">
-        <v>818.98126588</v>
+        <v>819.13175314</v>
       </c>
       <c r="F92">
-        <v>87.87941314</v>
+        <v>90.88385530999994</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3560,16 +3563,16 @@
         <v>0.02</v>
       </c>
       <c r="C93">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D93">
-        <v>903.66999905</v>
+        <v>906.86067902</v>
       </c>
       <c r="E93">
-        <v>818.82936496</v>
+        <v>818.98126588</v>
       </c>
       <c r="F93">
-        <v>84.84063408999998</v>
+        <v>87.87941314</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3580,16 +3583,16 @@
         <v>0.02</v>
       </c>
       <c r="C94">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D94">
-        <v>900.44266944</v>
+        <v>903.66999905</v>
       </c>
       <c r="E94">
-        <v>818.67603091</v>
+        <v>818.82936496</v>
       </c>
       <c r="F94">
-        <v>81.76663853000002</v>
+        <v>84.84063408999998</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3600,16 +3603,16 @@
         <v>0.02</v>
       </c>
       <c r="C95">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D95">
-        <v>897.17783486</v>
+        <v>900.44266944</v>
       </c>
       <c r="E95">
-        <v>818.5212441</v>
+        <v>818.67603091</v>
       </c>
       <c r="F95">
-        <v>78.65659075999997</v>
+        <v>81.76663853000002</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3620,16 +3623,16 @@
         <v>0.02</v>
       </c>
       <c r="C96">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D96">
-        <v>893.8746828</v>
+        <v>897.17783486</v>
       </c>
       <c r="E96">
-        <v>818.36498535</v>
+        <v>818.5212441</v>
       </c>
       <c r="F96">
-        <v>75.50969744999998</v>
+        <v>78.65659075999997</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3640,16 +3643,16 @@
         <v>0.02</v>
       </c>
       <c r="C97">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D97">
-        <v>890.53244321</v>
+        <v>893.8746828</v>
       </c>
       <c r="E97">
-        <v>818.20723428</v>
+        <v>818.36498535</v>
       </c>
       <c r="F97">
-        <v>72.32520893000003</v>
+        <v>75.50969744999998</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3660,16 +3663,16 @@
         <v>0.02</v>
       </c>
       <c r="C98">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D98">
-        <v>887.1503884</v>
+        <v>890.53244321</v>
       </c>
       <c r="E98">
-        <v>818.04796984</v>
+        <v>818.20723428</v>
       </c>
       <c r="F98">
-        <v>69.10241856000005</v>
+        <v>72.32520893000003</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3680,16 +3683,16 @@
         <v>0.02</v>
       </c>
       <c r="C99">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D99">
-        <v>883.72783263</v>
+        <v>887.1503884</v>
       </c>
       <c r="E99">
-        <v>817.8871729700001</v>
+        <v>818.04796984</v>
       </c>
       <c r="F99">
-        <v>65.84065965999991</v>
+        <v>69.10241856000005</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3700,16 +3703,16 @@
         <v>0.02</v>
       </c>
       <c r="C100">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D100">
-        <v>880.26413171</v>
+        <v>883.72783263</v>
       </c>
       <c r="E100">
-        <v>817.72481993</v>
+        <v>817.8871729700001</v>
       </c>
       <c r="F100">
-        <v>62.53931178000005</v>
+        <v>65.84065965999991</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3720,16 +3723,16 @@
         <v>0.02</v>
       </c>
       <c r="C101">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D101">
-        <v>876.7586826100001</v>
+        <v>880.26413171</v>
       </c>
       <c r="E101">
-        <v>817.56089219</v>
+        <v>817.72481993</v>
       </c>
       <c r="F101">
-        <v>59.19779042000005</v>
+        <v>62.53931178000005</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3740,16 +3743,16 @@
         <v>0.02</v>
       </c>
       <c r="C102">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D102">
-        <v>873.21092342</v>
+        <v>876.7586826100001</v>
       </c>
       <c r="E102">
-        <v>817.39536543</v>
+        <v>817.56089219</v>
       </c>
       <c r="F102">
-        <v>55.81555799</v>
+        <v>59.19779042000005</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3760,16 +3763,16 @@
         <v>0.02</v>
       </c>
       <c r="C103">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D103">
-        <v>869.62033276</v>
+        <v>873.21092342</v>
       </c>
       <c r="E103">
-        <v>817.22821814</v>
+        <v>817.39536543</v>
       </c>
       <c r="F103">
-        <v>52.39211462000003</v>
+        <v>55.81555799</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3780,16 +3783,16 @@
         <v>0.02</v>
       </c>
       <c r="C104">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D104">
-        <v>865.98642961</v>
+        <v>869.62033276</v>
       </c>
       <c r="E104">
-        <v>817.05942765</v>
+        <v>817.22821814</v>
       </c>
       <c r="F104">
-        <v>48.92700195999998</v>
+        <v>52.39211462000003</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3800,16 +3803,16 @@
         <v>0.02</v>
       </c>
       <c r="C105">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D105">
-        <v>862.308773</v>
+        <v>865.98642961</v>
       </c>
       <c r="E105">
-        <v>816.88897087</v>
+        <v>817.05942765</v>
       </c>
       <c r="F105">
-        <v>45.41980212999999</v>
+        <v>48.92700195999998</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3817,19 +3820,19 @@
         <v>110</v>
       </c>
       <c r="B106">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D106">
-        <v>926.9351673</v>
+        <v>862.308773</v>
       </c>
       <c r="E106">
-        <v>872.62179094</v>
+        <v>816.88897087</v>
       </c>
       <c r="F106">
-        <v>54.31337636000001</v>
+        <v>45.41980212999999</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3840,16 +3843,16 @@
         <v>0.025</v>
       </c>
       <c r="C107">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>923.96559109</v>
+        <v>926.9351673</v>
       </c>
       <c r="E107">
-        <v>846.36333283</v>
+        <v>872.62179094</v>
       </c>
       <c r="F107">
-        <v>77.60225825999999</v>
+        <v>54.31337636000001</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3860,16 +3863,16 @@
         <v>0.025</v>
       </c>
       <c r="C108">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D108">
-        <v>920.96569372</v>
+        <v>923.96559109</v>
       </c>
       <c r="E108">
-        <v>822.5404036899999</v>
+        <v>846.36333283</v>
       </c>
       <c r="F108">
-        <v>98.42529003000004</v>
+        <v>77.60225825999999</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3880,16 +3883,16 @@
         <v>0.025</v>
       </c>
       <c r="C109">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D109">
-        <v>917.93431593</v>
+        <v>920.96569372</v>
       </c>
       <c r="E109">
-        <v>812.57888339</v>
+        <v>822.5404036899999</v>
       </c>
       <c r="F109">
-        <v>105.35543254</v>
+        <v>98.42529003000004</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3900,16 +3903,16 @@
         <v>0.025</v>
       </c>
       <c r="C110">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D110">
-        <v>914.87034312</v>
+        <v>917.93431593</v>
       </c>
       <c r="E110">
-        <v>812.40536803</v>
+        <v>812.57888339</v>
       </c>
       <c r="F110">
-        <v>102.4649750900001</v>
+        <v>105.35543254</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3920,16 +3923,16 @@
         <v>0.025</v>
       </c>
       <c r="C111">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D111">
-        <v>911.77270776</v>
+        <v>914.87034312</v>
       </c>
       <c r="E111">
-        <v>812.23033639</v>
+        <v>812.40536803</v>
       </c>
       <c r="F111">
-        <v>99.54237136999996</v>
+        <v>102.4649750900001</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3940,16 +3943,16 @@
         <v>0.025</v>
       </c>
       <c r="C112">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D112">
-        <v>908.64038586</v>
+        <v>911.77270776</v>
       </c>
       <c r="E112">
-        <v>812.05377041</v>
+        <v>812.23033639</v>
       </c>
       <c r="F112">
-        <v>96.58661545000007</v>
+        <v>99.54237136999996</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3960,16 +3963,16 @@
         <v>0.025</v>
       </c>
       <c r="C113">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D113">
-        <v>905.47239958</v>
+        <v>908.64038586</v>
       </c>
       <c r="E113">
-        <v>811.87565101</v>
+        <v>812.05377041</v>
       </c>
       <c r="F113">
-        <v>93.59674857000005</v>
+        <v>96.58661545000007</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3980,16 +3983,16 @@
         <v>0.025</v>
       </c>
       <c r="C114">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D114">
-        <v>902.2678152</v>
+        <v>905.47239958</v>
       </c>
       <c r="E114">
-        <v>811.6959594800001</v>
+        <v>811.87565101</v>
       </c>
       <c r="F114">
-        <v>90.57185571999992</v>
+        <v>93.59674857000005</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4000,16 +4003,16 @@
         <v>0.025</v>
       </c>
       <c r="C115">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D115">
-        <v>899.02574307</v>
+        <v>902.2678152</v>
       </c>
       <c r="E115">
-        <v>811.51467661</v>
+        <v>811.6959594800001</v>
       </c>
       <c r="F115">
-        <v>87.51106645999994</v>
+        <v>90.57185571999992</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4020,16 +4023,16 @@
         <v>0.025</v>
       </c>
       <c r="C116">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D116">
-        <v>895.74533749</v>
+        <v>899.02574307</v>
       </c>
       <c r="E116">
-        <v>811.33178255</v>
+        <v>811.51467661</v>
       </c>
       <c r="F116">
-        <v>84.41355494000004</v>
+        <v>87.51106645999994</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4040,16 +4043,16 @@
         <v>0.025</v>
       </c>
       <c r="C117">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D117">
-        <v>892.4257954</v>
+        <v>895.74533749</v>
       </c>
       <c r="E117">
-        <v>811.1472578</v>
+        <v>811.33178255</v>
       </c>
       <c r="F117">
-        <v>81.27853759999994</v>
+        <v>84.41355494000004</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4060,16 +4063,16 @@
         <v>0.025</v>
       </c>
       <c r="C118">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D118">
-        <v>889.06635781</v>
+        <v>892.4257954</v>
       </c>
       <c r="E118">
-        <v>810.9610821799999</v>
+        <v>811.1472578</v>
       </c>
       <c r="F118">
-        <v>78.10527563000005</v>
+        <v>81.27853759999994</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4080,16 +4083,16 @@
         <v>0.025</v>
       </c>
       <c r="C119">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D119">
-        <v>885.66630735</v>
+        <v>889.06635781</v>
       </c>
       <c r="E119">
-        <v>810.77323528</v>
+        <v>810.9610821799999</v>
       </c>
       <c r="F119">
-        <v>74.89307207000002</v>
+        <v>78.10527563000005</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4100,16 +4103,16 @@
         <v>0.025</v>
       </c>
       <c r="C120">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D120">
-        <v>882.22496968</v>
+        <v>885.66630735</v>
       </c>
       <c r="E120">
-        <v>810.58369644</v>
+        <v>810.77323528</v>
       </c>
       <c r="F120">
-        <v>71.64127323999992</v>
+        <v>74.89307207000002</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4120,16 +4123,16 @@
         <v>0.025</v>
       </c>
       <c r="C121">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D121">
-        <v>878.74171203</v>
+        <v>882.22496968</v>
       </c>
       <c r="E121">
-        <v>810.39244481</v>
+        <v>810.58369644</v>
       </c>
       <c r="F121">
-        <v>68.34926722</v>
+        <v>71.64127323999992</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4140,16 +4143,16 @@
         <v>0.025</v>
       </c>
       <c r="C122">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D122">
-        <v>875.21594324</v>
+        <v>878.74171203</v>
       </c>
       <c r="E122">
-        <v>810.19945853</v>
+        <v>810.39244481</v>
       </c>
       <c r="F122">
-        <v>65.01648470999999</v>
+        <v>68.34926722</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4160,16 +4163,16 @@
         <v>0.025</v>
       </c>
       <c r="C123">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D123">
-        <v>871.64711369</v>
+        <v>875.21594324</v>
       </c>
       <c r="E123">
-        <v>810.004717</v>
+        <v>810.19945853</v>
       </c>
       <c r="F123">
-        <v>61.64239668999994</v>
+        <v>65.01648470999999</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4180,16 +4183,16 @@
         <v>0.025</v>
       </c>
       <c r="C124">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D124">
-        <v>868.03471455</v>
+        <v>871.64711369</v>
       </c>
       <c r="E124">
-        <v>809.80819748</v>
+        <v>810.004717</v>
       </c>
       <c r="F124">
-        <v>58.22651707</v>
+        <v>61.64239668999994</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4200,16 +4203,16 @@
         <v>0.025</v>
       </c>
       <c r="C125">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D125">
-        <v>864.37827779</v>
+        <v>868.03471455</v>
       </c>
       <c r="E125">
-        <v>809.60987773</v>
+        <v>809.80819748</v>
       </c>
       <c r="F125">
-        <v>54.76840005999998</v>
+        <v>58.22651707</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4220,16 +4223,16 @@
         <v>0.025</v>
       </c>
       <c r="C126">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D126">
-        <v>860.67737575</v>
+        <v>864.37827779</v>
       </c>
       <c r="E126">
-        <v>809.4097364100001</v>
+        <v>809.60987773</v>
       </c>
       <c r="F126">
-        <v>51.26763933999996</v>
+        <v>54.76840005999998</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4237,19 +4240,19 @@
         <v>131</v>
       </c>
       <c r="B127">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D127">
-        <v>925.61550485</v>
+        <v>860.67737575</v>
       </c>
       <c r="E127">
-        <v>862.52273243</v>
+        <v>809.4097364100001</v>
       </c>
       <c r="F127">
-        <v>63.09277241999996</v>
+        <v>51.26763933999996</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4260,16 +4263,16 @@
         <v>0.03</v>
       </c>
       <c r="C128">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>922.63795304</v>
+        <v>925.61550485</v>
       </c>
       <c r="E128">
-        <v>836.70796195</v>
+        <v>862.52273243</v>
       </c>
       <c r="F128">
-        <v>85.92999108999993</v>
+        <v>63.09277241999996</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4280,16 +4283,16 @@
         <v>0.03</v>
       </c>
       <c r="C129">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D129">
-        <v>919.62917181</v>
+        <v>922.63795304</v>
       </c>
       <c r="E129">
-        <v>813.51191705</v>
+        <v>836.70796195</v>
       </c>
       <c r="F129">
-        <v>106.11725476</v>
+        <v>85.92999108999993</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4300,16 +4303,16 @@
         <v>0.03</v>
       </c>
       <c r="C130">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D130">
-        <v>916.58800765</v>
+        <v>919.62917181</v>
       </c>
       <c r="E130">
-        <v>805.97886048</v>
+        <v>813.51191705</v>
       </c>
       <c r="F130">
-        <v>110.60914717</v>
+        <v>106.11725476</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4320,16 +4323,16 @@
         <v>0.03</v>
       </c>
       <c r="C131">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D131">
-        <v>913.51335419</v>
+        <v>916.58800765</v>
       </c>
       <c r="E131">
-        <v>805.78358378</v>
+        <v>805.97886048</v>
       </c>
       <c r="F131">
-        <v>107.72977041</v>
+        <v>110.60914717</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4340,16 +4343,16 @@
         <v>0.03</v>
       </c>
       <c r="C132">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D132">
-        <v>910.4041506999999</v>
+        <v>913.51335419</v>
       </c>
       <c r="E132">
-        <v>805.58672553</v>
+        <v>805.78358378</v>
       </c>
       <c r="F132">
-        <v>104.81742517</v>
+        <v>107.72977041</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4360,16 +4363,16 @@
         <v>0.03</v>
       </c>
       <c r="C133">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D133">
-        <v>907.25938252</v>
+        <v>910.4041506999999</v>
       </c>
       <c r="E133">
-        <v>805.38826885</v>
+        <v>805.58672553</v>
       </c>
       <c r="F133">
-        <v>101.87111367</v>
+        <v>104.81742517</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4380,16 +4383,16 @@
         <v>0.03</v>
       </c>
       <c r="C134">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D134">
-        <v>904.07808024</v>
+        <v>907.25938252</v>
       </c>
       <c r="E134">
-        <v>805.18819666</v>
+        <v>805.38826885</v>
       </c>
       <c r="F134">
-        <v>98.88988357999995</v>
+        <v>101.87111367</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4400,16 +4403,16 @@
         <v>0.03</v>
       </c>
       <c r="C135">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D135">
-        <v>900.85931928</v>
+        <v>904.07808024</v>
       </c>
       <c r="E135">
-        <v>804.98649171</v>
+        <v>805.18819666</v>
       </c>
       <c r="F135">
-        <v>95.87282757000003</v>
+        <v>98.88988357999995</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4420,16 +4423,16 @@
         <v>0.03</v>
       </c>
       <c r="C136">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D136">
-        <v>897.60221953</v>
+        <v>900.85931928</v>
       </c>
       <c r="E136">
-        <v>804.78313655</v>
+        <v>804.98649171</v>
       </c>
       <c r="F136">
-        <v>92.81908297999996</v>
+        <v>95.87282757000003</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4440,16 +4443,16 @@
         <v>0.03</v>
       </c>
       <c r="C137">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D137">
-        <v>894.3059451300001</v>
+        <v>897.60221953</v>
       </c>
       <c r="E137">
-        <v>804.57811353</v>
+        <v>804.78313655</v>
       </c>
       <c r="F137">
-        <v>89.72783160000006</v>
+        <v>92.81908297999996</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4460,16 +4463,16 @@
         <v>0.03</v>
       </c>
       <c r="C138">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D138">
-        <v>890.96970388</v>
+        <v>894.3059451300001</v>
       </c>
       <c r="E138">
-        <v>804.37140487</v>
+        <v>804.57811353</v>
       </c>
       <c r="F138">
-        <v>86.59829901000001</v>
+        <v>89.72783160000006</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4480,16 +4483,16 @@
         <v>0.03</v>
       </c>
       <c r="C139">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D139">
-        <v>887.59274743</v>
+        <v>890.96970388</v>
       </c>
       <c r="E139">
-        <v>804.16299248</v>
+        <v>804.37140487</v>
       </c>
       <c r="F139">
-        <v>83.42975495000007</v>
+        <v>86.59829901000001</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4500,16 +4503,16 @@
         <v>0.03</v>
       </c>
       <c r="C140">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D140">
-        <v>884.17436847</v>
+        <v>887.59274743</v>
       </c>
       <c r="E140">
-        <v>803.9528582</v>
+        <v>804.16299248</v>
       </c>
       <c r="F140">
-        <v>80.22151026999995</v>
+        <v>83.42975495000007</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4520,16 +4523,16 @@
         <v>0.03</v>
       </c>
       <c r="C141">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D141">
-        <v>880.7139054100001</v>
+        <v>884.17436847</v>
       </c>
       <c r="E141">
-        <v>803.7409836099999</v>
+        <v>803.9528582</v>
       </c>
       <c r="F141">
-        <v>76.97292180000011</v>
+        <v>80.22151026999995</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4540,16 +4543,16 @@
         <v>0.03</v>
       </c>
       <c r="C142">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D142">
-        <v>877.21073702</v>
+        <v>880.7139054100001</v>
       </c>
       <c r="E142">
-        <v>803.5273501</v>
+        <v>803.7409836099999</v>
       </c>
       <c r="F142">
-        <v>73.68338691999998</v>
+        <v>76.97292180000011</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4560,16 +4563,16 @@
         <v>0.03</v>
       </c>
       <c r="C143">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D143">
-        <v>873.66428411</v>
+        <v>877.21073702</v>
       </c>
       <c r="E143">
-        <v>803.31193888</v>
+        <v>803.5273501</v>
       </c>
       <c r="F143">
-        <v>70.35234523000008</v>
+        <v>73.68338691999998</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4580,16 +4583,16 @@
         <v>0.03</v>
       </c>
       <c r="C144">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D144">
-        <v>870.07400994</v>
+        <v>873.66428411</v>
       </c>
       <c r="E144">
-        <v>803.09473097</v>
+        <v>803.31193888</v>
       </c>
       <c r="F144">
-        <v>66.97927897</v>
+        <v>70.35234523000008</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4600,16 +4603,16 @@
         <v>0.03</v>
       </c>
       <c r="C145">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D145">
-        <v>866.4394185</v>
+        <v>870.07400994</v>
       </c>
       <c r="E145">
-        <v>802.87570721</v>
+        <v>803.09473097</v>
       </c>
       <c r="F145">
-        <v>63.56371129000001</v>
+        <v>66.97927897</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4620,16 +4623,16 @@
         <v>0.03</v>
       </c>
       <c r="C146">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D146">
-        <v>862.7600551199999</v>
+        <v>866.4394185</v>
       </c>
       <c r="E146">
-        <v>802.65484818</v>
+        <v>802.87570721</v>
       </c>
       <c r="F146">
-        <v>60.1052069399999</v>
+        <v>63.56371129000001</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4640,16 +4643,16 @@
         <v>0.03</v>
       </c>
       <c r="C147">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D147">
-        <v>859.03550577</v>
+        <v>862.7600551199999</v>
       </c>
       <c r="E147">
-        <v>802.4321343300001</v>
+        <v>802.65484818</v>
       </c>
       <c r="F147">
-        <v>56.60337143999993</v>
+        <v>60.1052069399999</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4657,19 +4660,19 @@
         <v>152</v>
       </c>
       <c r="B148">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D148">
-        <v>924.29107977</v>
+        <v>859.03550577</v>
       </c>
       <c r="E148">
-        <v>853.2358759700001</v>
+        <v>802.4321343300001</v>
       </c>
       <c r="F148">
-        <v>71.05520379999996</v>
+        <v>56.60337143999993</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4680,16 +4683,16 @@
         <v>0.035</v>
       </c>
       <c r="C149">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D149">
-        <v>921.30537686</v>
+        <v>924.29107977</v>
       </c>
       <c r="E149">
-        <v>827.86981056</v>
+        <v>853.2358759700001</v>
       </c>
       <c r="F149">
-        <v>93.4355663</v>
+        <v>71.05520379999996</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4700,16 +4703,16 @@
         <v>0.035</v>
       </c>
       <c r="C150">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D150">
-        <v>918.28751927</v>
+        <v>921.30537686</v>
       </c>
       <c r="E150">
-        <v>805.2813271700001</v>
+        <v>827.86981056</v>
       </c>
       <c r="F150">
-        <v>113.0061920999999</v>
+        <v>93.4355663</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4720,16 +4723,16 @@
         <v>0.035</v>
       </c>
       <c r="C151">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D151">
-        <v>915.23636182</v>
+        <v>918.28751927</v>
       </c>
       <c r="E151">
-        <v>799.81898481</v>
+        <v>805.2813271700001</v>
       </c>
       <c r="F151">
-        <v>115.41737701</v>
+        <v>113.0061920999999</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4740,16 +4743,16 @@
         <v>0.035</v>
       </c>
       <c r="C152">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D152">
-        <v>912.15080545</v>
+        <v>915.23636182</v>
       </c>
       <c r="E152">
-        <v>799.60751242</v>
+        <v>799.81898481</v>
       </c>
       <c r="F152">
-        <v>112.54329303</v>
+        <v>115.41737701</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4760,16 +4763,16 @@
         <v>0.035</v>
       </c>
       <c r="C153">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D153">
-        <v>909.02979815</v>
+        <v>912.15080545</v>
       </c>
       <c r="E153">
-        <v>799.39447789</v>
+        <v>799.60751242</v>
       </c>
       <c r="F153">
-        <v>109.6353202600001</v>
+        <v>112.54329303</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4780,16 +4783,16 @@
         <v>0.035</v>
       </c>
       <c r="C154">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D154">
-        <v>905.87233312</v>
+        <v>909.02979815</v>
       </c>
       <c r="E154">
-        <v>799.1798672899999</v>
+        <v>799.39447789</v>
       </c>
       <c r="F154">
-        <v>106.6924658300001</v>
+        <v>109.6353202600001</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4800,16 +4803,16 @@
         <v>0.035</v>
       </c>
       <c r="C155">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D155">
-        <v>902.6774508</v>
+        <v>905.87233312</v>
       </c>
       <c r="E155">
-        <v>798.96366661</v>
+        <v>799.1798672899999</v>
       </c>
       <c r="F155">
-        <v>103.71378419</v>
+        <v>106.6924658300001</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4820,16 +4823,16 @@
         <v>0.035</v>
       </c>
       <c r="C156">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D156">
-        <v>899.44423585</v>
+        <v>902.6774508</v>
       </c>
       <c r="E156">
-        <v>798.74586176</v>
+        <v>798.96366661</v>
       </c>
       <c r="F156">
-        <v>100.69837409</v>
+        <v>103.71378419</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4840,16 +4843,16 @@
         <v>0.035</v>
       </c>
       <c r="C157">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D157">
-        <v>896.17181823</v>
+        <v>899.44423585</v>
       </c>
       <c r="E157">
-        <v>798.52643856</v>
+        <v>798.74586176</v>
       </c>
       <c r="F157">
-        <v>97.64537967000001</v>
+        <v>100.69837409</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4860,16 +4863,16 @@
         <v>0.035</v>
       </c>
       <c r="C158">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D158">
-        <v>892.85937234</v>
+        <v>896.17181823</v>
       </c>
       <c r="E158">
-        <v>798.30538274</v>
+        <v>798.52643856</v>
       </c>
       <c r="F158">
-        <v>94.55398960000002</v>
+        <v>97.64537967000001</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4880,16 +4883,16 @@
         <v>0.035</v>
       </c>
       <c r="C159">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D159">
-        <v>889.5061167</v>
+        <v>892.85937234</v>
       </c>
       <c r="E159">
-        <v>798.08267998</v>
+        <v>798.30538274</v>
       </c>
       <c r="F159">
-        <v>91.42343672000004</v>
+        <v>94.55398960000002</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4900,16 +4903,16 @@
         <v>0.035</v>
       </c>
       <c r="C160">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D160">
-        <v>886.11131363</v>
+        <v>889.5061167</v>
       </c>
       <c r="E160">
-        <v>797.8583158500001</v>
+        <v>798.08267998</v>
       </c>
       <c r="F160">
-        <v>88.25299777999999</v>
+        <v>91.42343672000004</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -4920,16 +4923,16 @@
         <v>0.035</v>
       </c>
       <c r="C161">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D161">
-        <v>882.67426883</v>
+        <v>886.11131363</v>
       </c>
       <c r="E161">
-        <v>797.63227588</v>
+        <v>797.8583158500001</v>
       </c>
       <c r="F161">
-        <v>85.04199295000001</v>
+        <v>88.25299777999999</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4940,16 +4943,16 @@
         <v>0.035</v>
       </c>
       <c r="C162">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D162">
-        <v>879.19433099</v>
+        <v>882.67426883</v>
       </c>
       <c r="E162">
-        <v>797.4045455</v>
+        <v>797.63227588</v>
       </c>
       <c r="F162">
-        <v>81.78978548999999</v>
+        <v>85.04199295000001</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4960,16 +4963,16 @@
         <v>0.035</v>
       </c>
       <c r="C163">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D163">
-        <v>875.67089159</v>
+        <v>879.19433099</v>
       </c>
       <c r="E163">
-        <v>797.17511011</v>
+        <v>797.4045455</v>
       </c>
       <c r="F163">
-        <v>78.49578148000001</v>
+        <v>81.78978548999999</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -4980,16 +4983,16 @@
         <v>0.035</v>
       </c>
       <c r="C164">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D164">
-        <v>872.10338432</v>
+        <v>875.67089159</v>
       </c>
       <c r="E164">
-        <v>796.94395502</v>
+        <v>797.17511011</v>
       </c>
       <c r="F164">
-        <v>75.15942930000006</v>
+        <v>78.49578148000001</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -5000,16 +5003,16 @@
         <v>0.035</v>
       </c>
       <c r="C165">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D165">
-        <v>868.49128527</v>
+        <v>872.10338432</v>
       </c>
       <c r="E165">
-        <v>796.71106548</v>
+        <v>796.94395502</v>
       </c>
       <c r="F165">
-        <v>71.78021979000005</v>
+        <v>75.15942930000006</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5020,16 +5023,16 @@
         <v>0.035</v>
       </c>
       <c r="C166">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D166">
-        <v>864.83411127</v>
+        <v>868.49128527</v>
       </c>
       <c r="E166">
-        <v>796.4764267199999</v>
+        <v>796.71106548</v>
       </c>
       <c r="F166">
-        <v>68.35768455000004</v>
+        <v>71.78021979000005</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5040,16 +5043,16 @@
         <v>0.035</v>
       </c>
       <c r="C167">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D167">
-        <v>861.13142192</v>
+        <v>864.83411127</v>
       </c>
       <c r="E167">
-        <v>796.24002388</v>
+        <v>796.4764267199999</v>
       </c>
       <c r="F167">
-        <v>64.89139804000001</v>
+        <v>68.35768455000004</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5060,16 +5063,16 @@
         <v>0.035</v>
       </c>
       <c r="C168">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D168">
-        <v>857.3828170100001</v>
+        <v>861.13142192</v>
       </c>
       <c r="E168">
-        <v>796.00184208</v>
+        <v>796.24002388</v>
       </c>
       <c r="F168">
-        <v>61.38097493000009</v>
+        <v>64.89139804000001</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5077,19 +5080,19 @@
         <v>173</v>
       </c>
       <c r="B169">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D169">
-        <v>922.96164334</v>
+        <v>857.3828170100001</v>
       </c>
       <c r="E169">
-        <v>844.7608375</v>
+        <v>796.00184208</v>
       </c>
       <c r="F169">
-        <v>78.20080584000004</v>
+        <v>61.38097493000009</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5100,16 +5103,16 @@
         <v>0.04</v>
       </c>
       <c r="C170">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D170">
-        <v>919.96760922</v>
+        <v>922.96164334</v>
       </c>
       <c r="E170">
-        <v>819.84566353</v>
+        <v>844.7608375</v>
       </c>
       <c r="F170">
-        <v>100.12194569</v>
+        <v>78.20080584000004</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -5120,16 +5123,16 @@
         <v>0.04</v>
       </c>
       <c r="C171">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D171">
-        <v>916.9404796</v>
+        <v>919.96760922</v>
       </c>
       <c r="E171">
-        <v>797.84262462</v>
+        <v>819.84566353</v>
       </c>
       <c r="F171">
-        <v>119.09785498</v>
+        <v>100.12194569</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5140,16 +5143,16 @@
         <v>0.04</v>
       </c>
       <c r="C172">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D172">
-        <v>913.8791175600001</v>
+        <v>916.9404796</v>
       </c>
       <c r="E172">
-        <v>794.12563094</v>
+        <v>797.84262462</v>
       </c>
       <c r="F172">
-        <v>119.7534866200001</v>
+        <v>119.09785498</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -5160,16 +5163,16 @@
         <v>0.04</v>
       </c>
       <c r="C173">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D173">
-        <v>910.78243208</v>
+        <v>913.8791175600001</v>
       </c>
       <c r="E173">
-        <v>793.90335682</v>
+        <v>794.12563094</v>
       </c>
       <c r="F173">
-        <v>116.87907526</v>
+        <v>119.7534866200001</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5180,16 +5183,16 @@
         <v>0.04</v>
       </c>
       <c r="C174">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D174">
-        <v>907.64937947</v>
+        <v>910.78243208</v>
       </c>
       <c r="E174">
-        <v>793.67961155</v>
+        <v>793.90335682</v>
       </c>
       <c r="F174">
-        <v>113.96976792</v>
+        <v>116.87907526</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -5200,16 +5203,16 @@
         <v>0.04</v>
       </c>
       <c r="C175">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D175">
-        <v>904.47896296</v>
+        <v>907.64937947</v>
       </c>
       <c r="E175">
-        <v>793.45438509</v>
+        <v>793.67961155</v>
       </c>
       <c r="F175">
-        <v>111.02457787</v>
+        <v>113.96976792</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5220,16 +5223,16 @@
         <v>0.04</v>
       </c>
       <c r="C176">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D176">
-        <v>901.27023145</v>
+        <v>904.47896296</v>
       </c>
       <c r="E176">
-        <v>793.22766741</v>
+        <v>793.45438509</v>
       </c>
       <c r="F176">
-        <v>108.04256404</v>
+        <v>111.02457787</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -5240,16 +5243,16 @@
         <v>0.04</v>
       </c>
       <c r="C177">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D177">
-        <v>898.02227948</v>
+        <v>901.27023145</v>
       </c>
       <c r="E177">
-        <v>792.99944851</v>
+        <v>793.22766741</v>
       </c>
       <c r="F177">
-        <v>105.02283097</v>
+        <v>108.04256404</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5260,16 +5263,16 @@
         <v>0.04</v>
       </c>
       <c r="C178">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D178">
-        <v>894.73424894</v>
+        <v>898.02227948</v>
       </c>
       <c r="E178">
-        <v>792.76971843</v>
+        <v>792.99944851</v>
       </c>
       <c r="F178">
-        <v>101.96453051</v>
+        <v>105.02283097</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -5280,16 +5283,16 @@
         <v>0.04</v>
       </c>
       <c r="C179">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D179">
-        <v>891.4053232700001</v>
+        <v>894.73424894</v>
       </c>
       <c r="E179">
-        <v>792.5384672500001</v>
+        <v>792.76971843</v>
       </c>
       <c r="F179">
-        <v>98.86685602</v>
+        <v>101.96453051</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5300,16 +5303,16 @@
         <v>0.04</v>
       </c>
       <c r="C180">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D180">
-        <v>888.03473247</v>
+        <v>891.4053232700001</v>
       </c>
       <c r="E180">
-        <v>792.30568506</v>
+        <v>792.5384672500001</v>
       </c>
       <c r="F180">
-        <v>95.72904741000002</v>
+        <v>98.86685602</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5320,16 +5323,16 @@
         <v>0.04</v>
       </c>
       <c r="C181">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D181">
-        <v>884.6217509099999</v>
+        <v>888.03473247</v>
       </c>
       <c r="E181">
-        <v>792.07136202</v>
+        <v>792.30568506</v>
       </c>
       <c r="F181">
-        <v>92.55038888999991</v>
+        <v>95.72904741000002</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5340,16 +5343,16 @@
         <v>0.04</v>
       </c>
       <c r="C182">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D182">
-        <v>881.1656956099999</v>
+        <v>884.6217509099999</v>
       </c>
       <c r="E182">
-        <v>791.83548835</v>
+        <v>792.07136202</v>
       </c>
       <c r="F182">
-        <v>89.33020725999995</v>
+        <v>92.55038888999991</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5360,16 +5363,16 @@
         <v>0.04</v>
       </c>
       <c r="C183">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D183">
-        <v>877.66592768</v>
+        <v>881.1656956099999</v>
       </c>
       <c r="E183">
-        <v>791.59805433</v>
+        <v>791.83548835</v>
       </c>
       <c r="F183">
-        <v>86.06787335000001</v>
+        <v>89.33020725999995</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5380,16 +5383,16 @@
         <v>0.04</v>
       </c>
       <c r="C184">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D184">
-        <v>874.12185119</v>
+        <v>877.66592768</v>
       </c>
       <c r="E184">
-        <v>791.35905024</v>
+        <v>791.59805433</v>
       </c>
       <c r="F184">
-        <v>82.76280095000004</v>
+        <v>86.06787335000001</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5400,16 +5403,16 @@
         <v>0.04</v>
       </c>
       <c r="C185">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D185">
-        <v>870.53291288</v>
+        <v>874.12185119</v>
       </c>
       <c r="E185">
-        <v>791.11846656</v>
+        <v>791.35905024</v>
       </c>
       <c r="F185">
-        <v>79.41444632000002</v>
+        <v>82.76280095000004</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5420,16 +5423,16 @@
         <v>0.04</v>
       </c>
       <c r="C186">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D186">
-        <v>866.89860187</v>
+        <v>870.53291288</v>
       </c>
       <c r="E186">
-        <v>790.87629372</v>
+        <v>791.11846656</v>
       </c>
       <c r="F186">
-        <v>76.02230814999996</v>
+        <v>79.41444632000002</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -5440,16 +5443,16 @@
         <v>0.04</v>
       </c>
       <c r="C187">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D187">
-        <v>863.21844927</v>
+        <v>866.89860187</v>
       </c>
       <c r="E187">
-        <v>790.63252233</v>
+        <v>790.87629372</v>
       </c>
       <c r="F187">
-        <v>72.58592693999992</v>
+        <v>76.02230814999996</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -5460,16 +5463,16 @@
         <v>0.04</v>
       </c>
       <c r="C188">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D188">
-        <v>859.49202818</v>
+        <v>863.21844927</v>
       </c>
       <c r="E188">
-        <v>790.38714304</v>
+        <v>790.63252233</v>
       </c>
       <c r="F188">
-        <v>69.10488514000008</v>
+        <v>72.58592693999992</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -5480,16 +5483,16 @@
         <v>0.04</v>
       </c>
       <c r="C189">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D189">
-        <v>855.71895301</v>
+        <v>859.49202818</v>
       </c>
       <c r="E189">
-        <v>790.14014664</v>
+        <v>790.38714304</v>
       </c>
       <c r="F189">
-        <v>65.57880636999994</v>
+        <v>69.10488514000008</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -5497,19 +5500,19 @@
         <v>194</v>
       </c>
       <c r="B190">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D190">
-        <v>921.62693718</v>
+        <v>855.71895301</v>
       </c>
       <c r="E190">
-        <v>837.0769688300001</v>
+        <v>790.14014664</v>
       </c>
       <c r="F190">
-        <v>84.54996834999997</v>
+        <v>65.57880636999994</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -5520,16 +5523,16 @@
         <v>0.045</v>
       </c>
       <c r="C191">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D191">
-        <v>918.62438748</v>
+        <v>921.62693718</v>
       </c>
       <c r="E191">
-        <v>812.6126339</v>
+        <v>837.0769688300001</v>
       </c>
       <c r="F191">
-        <v>106.01175358</v>
+        <v>84.54996834999997</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -5540,16 +5543,16 @@
         <v>0.045</v>
       </c>
       <c r="C192">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D192">
-        <v>915.58778655</v>
+        <v>918.62438748</v>
       </c>
       <c r="E192">
-        <v>791.1714052900001</v>
+        <v>812.6126339</v>
       </c>
       <c r="F192">
-        <v>124.41638126</v>
+        <v>106.01175358</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -5560,16 +5563,16 @@
         <v>0.045</v>
       </c>
       <c r="C193">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D193">
-        <v>912.5160044</v>
+        <v>915.58778655</v>
       </c>
       <c r="E193">
-        <v>788.9090346200001</v>
+        <v>791.1714052900001</v>
       </c>
       <c r="F193">
-        <v>123.60696978</v>
+        <v>124.41638126</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -5580,16 +5583,16 @@
         <v>0.045</v>
       </c>
       <c r="C194">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D194">
-        <v>909.40795894</v>
+        <v>912.5160044</v>
       </c>
       <c r="E194">
-        <v>788.68093971</v>
+        <v>788.9090346200001</v>
       </c>
       <c r="F194">
-        <v>120.72701923</v>
+        <v>123.60696978</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -5600,16 +5603,16 @@
         <v>0.045</v>
       </c>
       <c r="C195">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D195">
-        <v>906.2626157</v>
+        <v>909.40795894</v>
       </c>
       <c r="E195">
-        <v>788.45152043</v>
+        <v>788.68093971</v>
       </c>
       <c r="F195">
-        <v>117.81109527</v>
+        <v>120.72701923</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -5620,16 +5623,16 @@
         <v>0.045</v>
       </c>
       <c r="C196">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D196">
-        <v>903.07898726</v>
+        <v>906.2626157</v>
       </c>
       <c r="E196">
-        <v>788.22077113</v>
+        <v>788.45152043</v>
       </c>
       <c r="F196">
-        <v>114.85821613</v>
+        <v>117.81109527</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -5640,16 +5643,16 @@
         <v>0.045</v>
       </c>
       <c r="C197">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D197">
-        <v>899.8561326</v>
+        <v>903.07898726</v>
       </c>
       <c r="E197">
-        <v>787.98868625</v>
+        <v>788.22077113</v>
       </c>
       <c r="F197">
-        <v>111.86744635</v>
+        <v>114.85821613</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -5660,16 +5663,16 @@
         <v>0.045</v>
       </c>
       <c r="C198">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D198">
-        <v>896.59315751</v>
+        <v>899.8561326</v>
       </c>
       <c r="E198">
-        <v>787.75526035</v>
+        <v>787.98868625</v>
       </c>
       <c r="F198">
-        <v>108.83789716</v>
+        <v>111.86744635</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -5680,16 +5683,16 @@
         <v>0.045</v>
       </c>
       <c r="C199">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D199">
-        <v>893.28921152</v>
+        <v>896.59315751</v>
       </c>
       <c r="E199">
-        <v>787.52048815</v>
+        <v>787.75526035</v>
       </c>
       <c r="F199">
-        <v>105.76872337</v>
+        <v>108.83789716</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -5700,16 +5703,16 @@
         <v>0.045</v>
       </c>
       <c r="C200">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D200">
-        <v>889.94349191</v>
+        <v>893.28921152</v>
       </c>
       <c r="E200">
-        <v>787.28436451</v>
+        <v>787.52048815</v>
       </c>
       <c r="F200">
-        <v>102.6591274</v>
+        <v>105.76872337</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -5720,16 +5723,16 @@
         <v>0.045</v>
       </c>
       <c r="C201">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D201">
-        <v>886.55524039</v>
+        <v>889.94349191</v>
       </c>
       <c r="E201">
-        <v>787.04688443</v>
+        <v>787.28436451</v>
       </c>
       <c r="F201">
-        <v>99.50835596000002</v>
+        <v>102.6591274</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -5740,16 +5743,16 @@
         <v>0.045</v>
       </c>
       <c r="C202">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D202">
-        <v>883.12374166</v>
+        <v>886.55524039</v>
       </c>
       <c r="E202">
-        <v>786.80804309</v>
+        <v>787.04688443</v>
       </c>
       <c r="F202">
-        <v>96.31569857</v>
+        <v>99.50835596000002</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -5760,16 +5763,16 @@
         <v>0.045</v>
       </c>
       <c r="C203">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D203">
-        <v>879.64832582</v>
+        <v>883.12374166</v>
       </c>
       <c r="E203">
-        <v>786.56783582</v>
+        <v>786.80804309</v>
       </c>
       <c r="F203">
-        <v>93.08048999999994</v>
+        <v>96.31569857</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -5780,16 +5783,16 @@
         <v>0.045</v>
       </c>
       <c r="C204">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D204">
-        <v>876.12836649</v>
+        <v>879.64832582</v>
       </c>
       <c r="E204">
-        <v>786.3262581499999</v>
+        <v>786.56783582</v>
       </c>
       <c r="F204">
-        <v>89.80210834000002</v>
+        <v>93.08048999999994</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -5800,16 +5803,16 @@
         <v>0.045</v>
       </c>
       <c r="C205">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D205">
-        <v>872.56328068</v>
+        <v>876.12836649</v>
       </c>
       <c r="E205">
-        <v>786.08330577</v>
+        <v>786.3262581499999</v>
       </c>
       <c r="F205">
-        <v>86.47997491000001</v>
+        <v>89.80210834000002</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -5820,16 +5823,16 @@
         <v>0.045</v>
       </c>
       <c r="C206">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D206">
-        <v>868.95252855</v>
+        <v>872.56328068</v>
       </c>
       <c r="E206">
-        <v>785.8389746</v>
+        <v>786.08330577</v>
       </c>
       <c r="F206">
-        <v>83.11355394999998</v>
+        <v>86.47997491000001</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -5840,16 +5843,16 @@
         <v>0.045</v>
       </c>
       <c r="C207">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D207">
-        <v>865.29561262</v>
+        <v>868.95252855</v>
       </c>
       <c r="E207">
-        <v>785.59326073</v>
+        <v>785.8389746</v>
       </c>
       <c r="F207">
-        <v>79.70235189000005</v>
+        <v>83.11355394999998</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -5860,16 +5863,16 @@
         <v>0.045</v>
       </c>
       <c r="C208">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D208">
-        <v>861.59207852</v>
+        <v>865.29561262</v>
       </c>
       <c r="E208">
-        <v>785.34616051</v>
+        <v>785.59326073</v>
       </c>
       <c r="F208">
-        <v>76.24591800999997</v>
+        <v>79.70235189000005</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -5880,16 +5883,16 @@
         <v>0.045</v>
       </c>
       <c r="C209">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D209">
-        <v>857.8415135400001</v>
+        <v>861.59207852</v>
       </c>
       <c r="E209">
-        <v>785.21813144</v>
+        <v>785.34616051</v>
       </c>
       <c r="F209">
-        <v>72.62338210000007</v>
+        <v>76.24591800999997</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -5900,16 +5903,16 @@
         <v>0.045</v>
       </c>
       <c r="C210">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D210">
-        <v>854.04354674</v>
+        <v>857.8415135400001</v>
       </c>
       <c r="E210">
         <v>785.21813144</v>
       </c>
       <c r="F210">
-        <v>68.82541530000003</v>
+        <v>72.62338210000007</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -5917,19 +5920,19 @@
         <v>215</v>
       </c>
       <c r="B211">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D211">
-        <v>920.28669325</v>
+        <v>854.04354674</v>
       </c>
       <c r="E211">
-        <v>830.14929326</v>
+        <v>785.21813144</v>
       </c>
       <c r="F211">
-        <v>90.13739998999995</v>
+        <v>68.82541530000003</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -5940,16 +5943,16 @@
         <v>0.05</v>
       </c>
       <c r="C212">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D212">
-        <v>917.27544073</v>
+        <v>920.28669325</v>
       </c>
       <c r="E212">
-        <v>806.13389847</v>
+        <v>830.14929326</v>
       </c>
       <c r="F212">
-        <v>111.1415422600001</v>
+        <v>90.13739998999995</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -5960,16 +5963,16 @@
         <v>0.05</v>
       </c>
       <c r="C213">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D213">
-        <v>914.22916409</v>
+        <v>917.27544073</v>
       </c>
       <c r="E213">
-        <v>786.01302642</v>
+        <v>806.13389847</v>
       </c>
       <c r="F213">
-        <v>128.2161376700001</v>
+        <v>111.1415422600001</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -5980,16 +5983,16 @@
         <v>0.05</v>
       </c>
       <c r="C214">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D214">
-        <v>911.14674195</v>
+        <v>914.22916409</v>
       </c>
       <c r="E214">
-        <v>785.21813144</v>
+        <v>786.01302642</v>
       </c>
       <c r="F214">
-        <v>125.92861051</v>
+        <v>128.2161376700001</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -6000,16 +6003,16 @@
         <v>0.05</v>
       </c>
       <c r="C215">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D215">
-        <v>908.02710121</v>
+        <v>911.14674195</v>
       </c>
       <c r="E215">
         <v>785.21813144</v>
       </c>
       <c r="F215">
-        <v>122.80896977</v>
+        <v>125.92861051</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -6020,16 +6023,16 @@
         <v>0.05</v>
       </c>
       <c r="C216">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D216">
-        <v>904.86921713</v>
+        <v>908.02710121</v>
       </c>
       <c r="E216">
         <v>785.21813144</v>
       </c>
       <c r="F216">
-        <v>119.6510856900001</v>
+        <v>122.80896977</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -6040,16 +6043,16 @@
         <v>0.05</v>
       </c>
       <c r="C217">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D217">
-        <v>901.67211169</v>
+        <v>904.86921713</v>
       </c>
       <c r="E217">
         <v>785.21813144</v>
       </c>
       <c r="F217">
-        <v>116.45398025</v>
+        <v>119.6510856900001</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -6060,16 +6063,16 @@
         <v>0.05</v>
       </c>
       <c r="C218">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D218">
-        <v>898.43485443</v>
+        <v>901.67211169</v>
       </c>
       <c r="E218">
         <v>785.21813144</v>
       </c>
       <c r="F218">
-        <v>113.21672299</v>
+        <v>116.45398025</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -6080,16 +6083,16 @@
         <v>0.05</v>
       </c>
       <c r="C219">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D219">
-        <v>895.15656196</v>
+        <v>898.43485443</v>
       </c>
       <c r="E219">
         <v>785.21813144</v>
       </c>
       <c r="F219">
-        <v>109.93843052</v>
+        <v>113.21672299</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -6100,16 +6103,16 @@
         <v>0.05</v>
       </c>
       <c r="C220">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D220">
-        <v>891.83639564</v>
+        <v>895.15656196</v>
       </c>
       <c r="E220">
         <v>785.21813144</v>
       </c>
       <c r="F220">
-        <v>106.6182642</v>
+        <v>109.93843052</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -6120,16 +6123,16 @@
         <v>0.05</v>
       </c>
       <c r="C221">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D221">
-        <v>888.4735634</v>
+        <v>891.83639564</v>
       </c>
       <c r="E221">
         <v>785.21813144</v>
       </c>
       <c r="F221">
-        <v>103.25543196</v>
+        <v>106.6182642</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -6140,16 +6143,16 @@
         <v>0.05</v>
       </c>
       <c r="C222">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D222">
-        <v>885.0673184</v>
+        <v>888.4735634</v>
       </c>
       <c r="E222">
         <v>785.21813144</v>
       </c>
       <c r="F222">
-        <v>99.84918696</v>
+        <v>103.25543196</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -6160,16 +6163,16 @@
         <v>0.05</v>
       </c>
       <c r="C223">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D223">
-        <v>881.61695849</v>
+        <v>885.0673184</v>
       </c>
       <c r="E223">
         <v>785.21813144</v>
       </c>
       <c r="F223">
-        <v>96.39882705000002</v>
+        <v>99.84918696</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -6180,16 +6183,16 @@
         <v>0.05</v>
       </c>
       <c r="C224">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D224">
-        <v>878.12182616</v>
+        <v>881.61695849</v>
       </c>
       <c r="E224">
         <v>785.21813144</v>
       </c>
       <c r="F224">
-        <v>92.90369471999998</v>
+        <v>96.39882705000002</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -6200,16 +6203,16 @@
         <v>0.05</v>
       </c>
       <c r="C225">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D225">
-        <v>874.5813080200001</v>
+        <v>878.12182616</v>
       </c>
       <c r="E225">
         <v>785.21813144</v>
       </c>
       <c r="F225">
-        <v>89.36317658000007</v>
+        <v>92.90369471999998</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -6220,16 +6223,16 @@
         <v>0.05</v>
       </c>
       <c r="C226">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D226">
-        <v>870.99483444</v>
+        <v>874.5813080200001</v>
       </c>
       <c r="E226">
         <v>785.21813144</v>
       </c>
       <c r="F226">
-        <v>85.776703</v>
+        <v>89.36317658000007</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -6240,16 +6243,16 @@
         <v>0.05</v>
       </c>
       <c r="C227">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D227">
-        <v>867.36187919</v>
+        <v>870.99483444</v>
       </c>
       <c r="E227">
         <v>785.21813144</v>
       </c>
       <c r="F227">
-        <v>82.14374774999999</v>
+        <v>85.776703</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -6260,16 +6263,16 @@
         <v>0.05</v>
       </c>
       <c r="C228">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D228">
-        <v>863.68195925</v>
+        <v>867.36187919</v>
       </c>
       <c r="E228">
         <v>785.21813144</v>
       </c>
       <c r="F228">
-        <v>78.46382781</v>
+        <v>82.14374774999999</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -6280,16 +6283,16 @@
         <v>0.05</v>
       </c>
       <c r="C229">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D229">
-        <v>859.9546348600001</v>
+        <v>863.68195925</v>
       </c>
       <c r="E229">
         <v>785.21813144</v>
       </c>
       <c r="F229">
-        <v>74.73650342000008</v>
+        <v>78.46382781</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -6300,16 +6303,16 @@
         <v>0.05</v>
       </c>
       <c r="C230">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D230">
-        <v>856.17950661</v>
+        <v>859.9546348600001</v>
       </c>
       <c r="E230">
         <v>785.21813144</v>
       </c>
       <c r="F230">
-        <v>70.96137517</v>
+        <v>74.73650342000008</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -6320,16 +6323,16 @@
         <v>0.05</v>
       </c>
       <c r="C231">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D231">
-        <v>852.35622045</v>
+        <v>856.17950661</v>
       </c>
       <c r="E231">
         <v>785.21813144</v>
       </c>
       <c r="F231">
-        <v>67.13808901000004</v>
+        <v>70.96137517</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -6337,19 +6340,19 @@
         <v>236</v>
       </c>
       <c r="B232">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D232">
-        <v>918.94063326</v>
+        <v>852.35622045</v>
       </c>
       <c r="E232">
-        <v>823.9336947100001</v>
+        <v>785.21813144</v>
       </c>
       <c r="F232">
-        <v>95.00693854999997</v>
+        <v>67.13808901000004</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -6360,16 +6363,16 @@
         <v>0.055</v>
       </c>
       <c r="C233">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D233">
-        <v>915.92048664</v>
+        <v>918.94063326</v>
       </c>
       <c r="E233">
-        <v>802.49256781</v>
+        <v>823.9336947100001</v>
       </c>
       <c r="F233">
-        <v>113.4279188300001</v>
+        <v>95.00693854999997</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -6380,16 +6383,16 @@
         <v>0.055</v>
       </c>
       <c r="C234">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D234">
-        <v>912.86432617</v>
+        <v>915.92048664</v>
       </c>
       <c r="E234">
-        <v>785.6717513</v>
+        <v>802.49256781</v>
       </c>
       <c r="F234">
-        <v>127.19257487</v>
+        <v>113.4279188300001</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -6400,16 +6403,16 @@
         <v>0.055</v>
       </c>
       <c r="C235">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D235">
-        <v>909.77103973</v>
+        <v>912.86432617</v>
       </c>
       <c r="E235">
-        <v>785.21813144</v>
+        <v>785.6717513</v>
       </c>
       <c r="F235">
-        <v>124.55290829</v>
+        <v>127.19257487</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -6420,16 +6423,16 @@
         <v>0.055</v>
       </c>
       <c r="C236">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D236">
-        <v>906.63956388</v>
+        <v>909.77103973</v>
       </c>
       <c r="E236">
         <v>785.21813144</v>
       </c>
       <c r="F236">
-        <v>121.42143244</v>
+        <v>124.55290829</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -6440,16 +6443,16 @@
         <v>0.055</v>
       </c>
       <c r="C237">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D237">
-        <v>903.46888353</v>
+        <v>906.63956388</v>
       </c>
       <c r="E237">
         <v>785.21813144</v>
       </c>
       <c r="F237">
-        <v>118.25075209</v>
+        <v>121.42143244</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -6460,16 +6463,16 @@
         <v>0.055</v>
       </c>
       <c r="C238">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D238">
-        <v>900.25803145</v>
+        <v>903.46888353</v>
       </c>
       <c r="E238">
         <v>785.21813144</v>
       </c>
       <c r="F238">
-        <v>115.03990001</v>
+        <v>118.25075209</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -6480,16 +6483,16 @@
         <v>0.055</v>
       </c>
       <c r="C239">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D239">
-        <v>897.00608772</v>
+        <v>900.25803145</v>
       </c>
       <c r="E239">
         <v>785.21813144</v>
       </c>
       <c r="F239">
-        <v>111.78795628</v>
+        <v>115.03990001</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -6500,16 +6503,16 @@
         <v>0.055</v>
       </c>
       <c r="C240">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D240">
-        <v>893.7121796</v>
+        <v>897.00608772</v>
       </c>
       <c r="E240">
         <v>785.21813144</v>
       </c>
       <c r="F240">
-        <v>108.49404816</v>
+        <v>111.78795628</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -6520,16 +6523,16 @@
         <v>0.055</v>
       </c>
       <c r="C241">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D241">
-        <v>890.37548063</v>
+        <v>893.7121796</v>
       </c>
       <c r="E241">
         <v>785.21813144</v>
       </c>
       <c r="F241">
-        <v>105.15734919</v>
+        <v>108.49404816</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -6540,16 +6543,16 @@
         <v>0.055</v>
       </c>
       <c r="C242">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D242">
-        <v>886.9952107300001</v>
+        <v>890.37548063</v>
       </c>
       <c r="E242">
         <v>785.21813144</v>
       </c>
       <c r="F242">
-        <v>101.7770792900001</v>
+        <v>105.15734919</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -6560,16 +6563,16 @@
         <v>0.055</v>
       </c>
       <c r="C243">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D243">
-        <v>883.57063455</v>
+        <v>886.9952107300001</v>
       </c>
       <c r="E243">
         <v>785.21813144</v>
       </c>
       <c r="F243">
-        <v>98.35250311000004</v>
+        <v>101.7770792900001</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -6580,16 +6583,16 @@
         <v>0.055</v>
       </c>
       <c r="C244">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D244">
-        <v>880.10106348</v>
+        <v>883.57063455</v>
       </c>
       <c r="E244">
         <v>785.21813144</v>
       </c>
       <c r="F244">
-        <v>94.88293204000001</v>
+        <v>98.35250311000004</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -6600,16 +6603,16 @@
         <v>0.055</v>
       </c>
       <c r="C245">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D245">
-        <v>876.5858527300001</v>
+        <v>880.10106348</v>
       </c>
       <c r="E245">
         <v>785.21813144</v>
       </c>
       <c r="F245">
-        <v>91.36772129000008</v>
+        <v>94.88293204000001</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -6620,16 +6623,16 @@
         <v>0.055</v>
       </c>
       <c r="C246">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D246">
-        <v>873.02440217</v>
+        <v>876.5858527300001</v>
       </c>
       <c r="E246">
         <v>785.21813144</v>
       </c>
       <c r="F246">
-        <v>87.80627073000005</v>
+        <v>91.36772129000008</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -6640,16 +6643,16 @@
         <v>0.055</v>
       </c>
       <c r="C247">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D247">
-        <v>869.41615613</v>
+        <v>873.02440217</v>
       </c>
       <c r="E247">
         <v>785.21813144</v>
       </c>
       <c r="F247">
-        <v>84.19802469000001</v>
+        <v>87.80627073000005</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -6660,16 +6663,16 @@
         <v>0.055</v>
       </c>
       <c r="C248">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D248">
-        <v>865.76060248</v>
+        <v>869.41615613</v>
       </c>
       <c r="E248">
         <v>785.21813144</v>
       </c>
       <c r="F248">
-        <v>80.54247104000001</v>
+        <v>84.19802469000001</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -6680,16 +6683,16 @@
         <v>0.055</v>
       </c>
       <c r="C249">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D249">
-        <v>862.05727265</v>
+        <v>865.76060248</v>
       </c>
       <c r="E249">
         <v>785.21813144</v>
       </c>
       <c r="F249">
-        <v>76.83914120999998</v>
+        <v>80.54247104000001</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -6700,16 +6703,16 @@
         <v>0.055</v>
       </c>
       <c r="C250">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D250">
-        <v>858.30574114</v>
+        <v>862.05727265</v>
       </c>
       <c r="E250">
         <v>785.21813144</v>
       </c>
       <c r="F250">
-        <v>73.08760970000003</v>
+        <v>76.83914120999998</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -6720,16 +6723,16 @@
         <v>0.055</v>
       </c>
       <c r="C251">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D251">
-        <v>854.5056254</v>
+        <v>858.30574114</v>
       </c>
       <c r="E251">
         <v>785.21813144</v>
       </c>
       <c r="F251">
-        <v>69.28749396000001</v>
+        <v>73.08760970000003</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -6740,16 +6743,16 @@
         <v>0.055</v>
       </c>
       <c r="C252">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D252">
-        <v>850.65658538</v>
+        <v>854.5056254</v>
       </c>
       <c r="E252">
         <v>785.21813144</v>
       </c>
       <c r="F252">
-        <v>65.43845394000004</v>
+        <v>69.28749396000001</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -6757,19 +6760,19 @@
         <v>257</v>
       </c>
       <c r="B253">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D253">
-        <v>917.58846982</v>
+        <v>850.65658538</v>
       </c>
       <c r="E253">
-        <v>820.73950728</v>
+        <v>785.21813144</v>
       </c>
       <c r="F253">
-        <v>96.84896254</v>
+        <v>65.43845394000004</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -6780,16 +6783,16 @@
         <v>0.06</v>
       </c>
       <c r="C254">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D254">
-        <v>914.55923304</v>
+        <v>917.58846982</v>
       </c>
       <c r="E254">
-        <v>802.3050062999999</v>
+        <v>820.73950728</v>
       </c>
       <c r="F254">
-        <v>112.25422674</v>
+        <v>96.84896254</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -6800,16 +6803,16 @@
         <v>0.06</v>
       </c>
       <c r="C255">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D255">
-        <v>911.49297643</v>
+        <v>914.55923304</v>
       </c>
       <c r="E255">
-        <v>785.3236793</v>
+        <v>802.3050062999999</v>
       </c>
       <c r="F255">
-        <v>126.16929713</v>
+        <v>112.25422674</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -6820,16 +6823,16 @@
         <v>0.06</v>
       </c>
       <c r="C256">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D256">
-        <v>908.3885970600001</v>
+        <v>911.49297643</v>
       </c>
       <c r="E256">
-        <v>785.21813144</v>
+        <v>785.3236793</v>
       </c>
       <c r="F256">
-        <v>123.1704656200001</v>
+        <v>126.16929713</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -6840,16 +6843,16 @@
         <v>0.06</v>
       </c>
       <c r="C257">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D257">
-        <v>905.24504153</v>
+        <v>908.3885970600001</v>
       </c>
       <c r="E257">
         <v>785.21813144</v>
       </c>
       <c r="F257">
-        <v>120.02691009</v>
+        <v>123.1704656200001</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -6860,16 +6863,16 @@
         <v>0.06</v>
       </c>
       <c r="C258">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D258">
-        <v>902.06130508</v>
+        <v>905.24504153</v>
       </c>
       <c r="E258">
         <v>785.21813144</v>
       </c>
       <c r="F258">
-        <v>116.84317364</v>
+        <v>120.02691009</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -6880,16 +6883,16 @@
         <v>0.06</v>
       </c>
       <c r="C259">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D259">
-        <v>898.8364315699999</v>
+        <v>902.06130508</v>
       </c>
       <c r="E259">
         <v>785.21813144</v>
       </c>
       <c r="F259">
-        <v>113.61830013</v>
+        <v>116.84317364</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -6900,16 +6903,16 @@
         <v>0.06</v>
       </c>
       <c r="C260">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D260">
-        <v>895.5695113199999</v>
+        <v>898.8364315699999</v>
       </c>
       <c r="E260">
         <v>785.21813144</v>
       </c>
       <c r="F260">
-        <v>110.35137988</v>
+        <v>113.61830013</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -6920,16 +6923,16 @@
         <v>0.06</v>
       </c>
       <c r="C261">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D261">
-        <v>892.25968413</v>
+        <v>895.5695113199999</v>
       </c>
       <c r="E261">
         <v>785.21813144</v>
       </c>
       <c r="F261">
-        <v>107.04155269</v>
+        <v>110.35137988</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -6940,16 +6943,16 @@
         <v>0.06</v>
       </c>
       <c r="C262">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D262">
-        <v>888.90613537</v>
+        <v>892.25968413</v>
       </c>
       <c r="E262">
         <v>785.21813144</v>
       </c>
       <c r="F262">
-        <v>103.68800393</v>
+        <v>107.04155269</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -6960,16 +6963,16 @@
         <v>0.06</v>
       </c>
       <c r="C263">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D263">
-        <v>885.50809644</v>
+        <v>888.90613537</v>
       </c>
       <c r="E263">
         <v>785.21813144</v>
       </c>
       <c r="F263">
-        <v>100.2899650000001</v>
+        <v>103.68800393</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -6980,16 +6983,16 @@
         <v>0.06</v>
       </c>
       <c r="C264">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D264">
-        <v>882.06484612</v>
+        <v>885.50809644</v>
       </c>
       <c r="E264">
         <v>785.21813144</v>
       </c>
       <c r="F264">
-        <v>96.84671467999999</v>
+        <v>100.2899650000001</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -7000,16 +7003,16 @@
         <v>0.06</v>
       </c>
       <c r="C265">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D265">
-        <v>878.57570789</v>
+        <v>882.06484612</v>
       </c>
       <c r="E265">
         <v>785.21813144</v>
       </c>
       <c r="F265">
-        <v>93.35757645000001</v>
+        <v>96.84671467999999</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -7020,16 +7023,16 @@
         <v>0.06</v>
       </c>
       <c r="C266">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D266">
-        <v>875.04005058</v>
+        <v>878.57570789</v>
       </c>
       <c r="E266">
         <v>785.21813144</v>
       </c>
       <c r="F266">
-        <v>89.82191913999998</v>
+        <v>93.35757645000001</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -7040,16 +7043,16 @@
         <v>0.06</v>
       </c>
       <c r="C267">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D267">
-        <v>871.4572879900001</v>
+        <v>875.04005058</v>
       </c>
       <c r="E267">
         <v>785.21813144</v>
       </c>
       <c r="F267">
-        <v>86.23915655000008</v>
+        <v>89.82191913999998</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7060,16 +7063,16 @@
         <v>0.06</v>
       </c>
       <c r="C268">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D268">
-        <v>867.8268785400001</v>
+        <v>871.4572879900001</v>
       </c>
       <c r="E268">
         <v>785.21813144</v>
       </c>
       <c r="F268">
-        <v>82.60874710000007</v>
+        <v>86.23915655000008</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -7080,16 +7083,16 @@
         <v>0.06</v>
       </c>
       <c r="C269">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D269">
-        <v>864.14832467</v>
+        <v>867.8268785400001</v>
       </c>
       <c r="E269">
         <v>785.21813144</v>
       </c>
       <c r="F269">
-        <v>78.93019322999999</v>
+        <v>82.60874710000007</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7100,16 +7103,16 @@
         <v>0.06</v>
       </c>
       <c r="C270">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D270">
-        <v>860.42117268</v>
+        <v>864.14832467</v>
       </c>
       <c r="E270">
         <v>785.21813144</v>
       </c>
       <c r="F270">
-        <v>75.20304124000006</v>
+        <v>78.93019322999999</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -7120,16 +7123,16 @@
         <v>0.06</v>
       </c>
       <c r="C271">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D271">
-        <v>856.64501229</v>
+        <v>860.42117268</v>
       </c>
       <c r="E271">
         <v>785.21813144</v>
       </c>
       <c r="F271">
-        <v>71.42688084999997</v>
+        <v>75.20304124000006</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -7140,16 +7143,16 @@
         <v>0.06</v>
       </c>
       <c r="C272">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D272">
-        <v>852.8194766</v>
+        <v>856.64501229</v>
       </c>
       <c r="E272">
         <v>785.21813144</v>
       </c>
       <c r="F272">
-        <v>67.60134516000005</v>
+        <v>71.42688084999997</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -7160,16 +7163,16 @@
         <v>0.06</v>
       </c>
       <c r="C273">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D273">
-        <v>848.9442414599999</v>
+        <v>852.8194766</v>
       </c>
       <c r="E273">
         <v>785.21813144</v>
       </c>
       <c r="F273">
-        <v>63.72611001999996</v>
+        <v>67.60134516000005</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -7177,19 +7180,19 @@
         <v>278</v>
       </c>
       <c r="B274">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="C274">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D274">
-        <v>916.22990347</v>
+        <v>848.9442414599999</v>
       </c>
       <c r="E274">
-        <v>820.73950751</v>
+        <v>785.21813144</v>
       </c>
       <c r="F274">
-        <v>95.49039596</v>
+        <v>63.72611001999996</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -7200,16 +7203,16 @@
         <v>0.065</v>
       </c>
       <c r="C275">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D275">
-        <v>913.19137755</v>
+        <v>916.22990347</v>
       </c>
       <c r="E275">
-        <v>802.11354998</v>
+        <v>820.73950751</v>
       </c>
       <c r="F275">
-        <v>111.07782757</v>
+        <v>95.49039596</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -7220,16 +7223,16 @@
         <v>0.065</v>
       </c>
       <c r="C276">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D276">
-        <v>910.11480792</v>
+        <v>913.19137755</v>
       </c>
       <c r="E276">
-        <v>785.21813144</v>
+        <v>802.11354998</v>
       </c>
       <c r="F276">
-        <v>124.89667648</v>
+        <v>111.07782757</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -7240,16 +7243,16 @@
         <v>0.065</v>
       </c>
       <c r="C277">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D277">
-        <v>906.9991025</v>
+        <v>910.11480792</v>
       </c>
       <c r="E277">
         <v>785.21813144</v>
       </c>
       <c r="F277">
-        <v>121.7809710600001</v>
+        <v>124.89667648</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -7260,16 +7263,16 @@
         <v>0.065</v>
       </c>
       <c r="C278">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D278">
-        <v>903.8432180999999</v>
+        <v>906.9991025</v>
       </c>
       <c r="E278">
         <v>785.21813144</v>
       </c>
       <c r="F278">
-        <v>118.62508666</v>
+        <v>121.7809710600001</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -7280,16 +7283,16 @@
         <v>0.065</v>
       </c>
       <c r="C279">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D279">
-        <v>900.64616074</v>
+        <v>903.8432180999999</v>
       </c>
       <c r="E279">
         <v>785.21813144</v>
       </c>
       <c r="F279">
-        <v>115.4280293</v>
+        <v>118.62508666</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -7300,16 +7303,16 @@
         <v>0.065</v>
       </c>
       <c r="C280">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D280">
-        <v>897.4069851</v>
+        <v>900.64616074</v>
       </c>
       <c r="E280">
         <v>785.21813144</v>
       </c>
       <c r="F280">
-        <v>112.1888536600001</v>
+        <v>115.4280293</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -7320,16 +7323,16 @@
         <v>0.065</v>
       </c>
       <c r="C281">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D281">
-        <v>894.1247942799999</v>
+        <v>897.4069851</v>
       </c>
       <c r="E281">
         <v>785.21813144</v>
       </c>
       <c r="F281">
-        <v>108.90666284</v>
+        <v>112.1888536600001</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -7340,16 +7343,16 @@
         <v>0.065</v>
       </c>
       <c r="C282">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D282">
-        <v>890.79873897</v>
+        <v>894.1247942799999</v>
       </c>
       <c r="E282">
         <v>785.21813144</v>
       </c>
       <c r="F282">
-        <v>105.5806075300001</v>
+        <v>108.90666284</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7360,16 +7363,16 @@
         <v>0.065</v>
       </c>
       <c r="C283">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D283">
-        <v>887.42801751</v>
+        <v>890.79873897</v>
       </c>
       <c r="E283">
         <v>785.21813144</v>
       </c>
       <c r="F283">
-        <v>102.20988607</v>
+        <v>105.5806075300001</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -7380,16 +7383,16 @@
         <v>0.065</v>
       </c>
       <c r="C284">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D284">
-        <v>884.0118734599999</v>
+        <v>887.42801751</v>
       </c>
       <c r="E284">
         <v>785.21813144</v>
       </c>
       <c r="F284">
-        <v>98.79374201999997</v>
+        <v>102.20988607</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -7400,16 +7403,16 @@
         <v>0.065</v>
       </c>
       <c r="C285">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D285">
-        <v>880.54959934</v>
+        <v>884.0118734599999</v>
       </c>
       <c r="E285">
         <v>785.21813144</v>
       </c>
       <c r="F285">
-        <v>95.33146790000001</v>
+        <v>98.79374201999997</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -7420,16 +7423,16 @@
         <v>0.065</v>
       </c>
       <c r="C286">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D286">
-        <v>877.04053183</v>
+        <v>880.54959934</v>
       </c>
       <c r="E286">
         <v>785.21813144</v>
       </c>
       <c r="F286">
-        <v>91.82240038999998</v>
+        <v>95.33146790000001</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -7440,16 +7443,16 @@
         <v>0.065</v>
       </c>
       <c r="C287">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D287">
-        <v>873.48405384</v>
+        <v>877.04053183</v>
       </c>
       <c r="E287">
         <v>785.21813144</v>
       </c>
       <c r="F287">
-        <v>88.26592240000002</v>
+        <v>91.82240038999998</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -7460,16 +7463,16 @@
         <v>0.065</v>
       </c>
       <c r="C288">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D288">
-        <v>869.87959332</v>
+        <v>873.48405384</v>
       </c>
       <c r="E288">
         <v>785.21813144</v>
       </c>
       <c r="F288">
-        <v>84.66146188000005</v>
+        <v>88.26592240000002</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -7480,16 +7483,16 @@
         <v>0.065</v>
       </c>
       <c r="C289">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D289">
-        <v>866.22662323</v>
+        <v>869.87959332</v>
       </c>
       <c r="E289">
         <v>785.21813144</v>
       </c>
       <c r="F289">
-        <v>81.00849178999999</v>
+        <v>84.66146188000005</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -7500,16 +7503,16 @@
         <v>0.065</v>
       </c>
       <c r="C290">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D290">
-        <v>862.52466087</v>
+        <v>866.22662323</v>
       </c>
       <c r="E290">
         <v>785.21813144</v>
       </c>
       <c r="F290">
-        <v>77.30652943000007</v>
+        <v>81.00849178999999</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -7520,16 +7523,16 @@
         <v>0.065</v>
       </c>
       <c r="C291">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D291">
-        <v>858.7732678900001</v>
+        <v>862.52466087</v>
       </c>
       <c r="E291">
         <v>785.21813144</v>
       </c>
       <c r="F291">
-        <v>73.55513645000008</v>
+        <v>77.30652943000007</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -7540,16 +7543,16 @@
         <v>0.065</v>
       </c>
       <c r="C292">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D292">
-        <v>854.97204975</v>
+        <v>858.7732678900001</v>
       </c>
       <c r="E292">
         <v>785.21813144</v>
       </c>
       <c r="F292">
-        <v>69.75391831000002</v>
+        <v>73.55513645000008</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -7560,16 +7563,16 @@
         <v>0.065</v>
       </c>
       <c r="C293">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D293">
-        <v>851.12065547</v>
+        <v>854.97204975</v>
       </c>
       <c r="E293">
         <v>785.21813144</v>
       </c>
       <c r="F293">
-        <v>65.90252403</v>
+        <v>69.75391831000002</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -7580,16 +7583,16 @@
         <v>0.065</v>
       </c>
       <c r="C294">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D294">
-        <v>847.21877731</v>
+        <v>851.12065547</v>
       </c>
       <c r="E294">
         <v>785.21813144</v>
       </c>
       <c r="F294">
-        <v>62.00064586999997</v>
+        <v>65.90252403</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -7597,19 +7600,19 @@
         <v>299</v>
       </c>
       <c r="B295">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="C295">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D295">
-        <v>914.86462496</v>
+        <v>847.21877731</v>
       </c>
       <c r="E295">
-        <v>820.73950751</v>
+        <v>785.21813144</v>
       </c>
       <c r="F295">
-        <v>94.12511745000006</v>
+        <v>62.00064586999997</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -7620,16 +7623,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C296">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D296">
-        <v>911.81660576</v>
+        <v>914.86462496</v>
       </c>
       <c r="E296">
-        <v>801.91807636</v>
+        <v>820.73950751</v>
       </c>
       <c r="F296">
-        <v>109.8985294</v>
+        <v>94.12511745000006</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -7640,16 +7643,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C297">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D297">
-        <v>908.72950281</v>
+        <v>911.81660576</v>
       </c>
       <c r="E297">
-        <v>785.21813144</v>
+        <v>801.91807636</v>
       </c>
       <c r="F297">
-        <v>123.51137137</v>
+        <v>109.8985294</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -7660,16 +7663,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C298">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D298">
-        <v>905.6022338400001</v>
+        <v>908.72950281</v>
       </c>
       <c r="E298">
         <v>785.21813144</v>
       </c>
       <c r="F298">
-        <v>120.3841024000001</v>
+        <v>123.51137137</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -7680,16 +7683,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C299">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D299">
-        <v>902.43376668</v>
+        <v>905.6022338400001</v>
       </c>
       <c r="E299">
         <v>785.21813144</v>
       </c>
       <c r="F299">
-        <v>117.21563524</v>
+        <v>120.3841024000001</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -7700,16 +7703,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C300">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D300">
-        <v>899.22311861</v>
+        <v>902.43376668</v>
       </c>
       <c r="E300">
         <v>785.21813144</v>
       </c>
       <c r="F300">
-        <v>114.00498717</v>
+        <v>117.21563524</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -7720,16 +7723,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C301">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D301">
-        <v>895.96935616</v>
+        <v>899.22311861</v>
       </c>
       <c r="E301">
         <v>785.21813144</v>
       </c>
       <c r="F301">
-        <v>110.75122472</v>
+        <v>114.00498717</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -7740,16 +7743,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C302">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D302">
-        <v>892.67159439</v>
+        <v>895.96935616</v>
       </c>
       <c r="E302">
         <v>785.21813144</v>
       </c>
       <c r="F302">
-        <v>107.45346295</v>
+        <v>110.75122472</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -7760,16 +7763,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C303">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D303">
-        <v>889.3289964000001</v>
+        <v>892.67159439</v>
       </c>
       <c r="E303">
         <v>785.21813144</v>
       </c>
       <c r="F303">
-        <v>104.1108649600001</v>
+        <v>107.45346295</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -7780,16 +7783,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C304">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D304">
-        <v>885.94077315</v>
+        <v>889.3289964000001</v>
       </c>
       <c r="E304">
         <v>785.21813144</v>
       </c>
       <c r="F304">
-        <v>100.7226417100001</v>
+        <v>104.1108649600001</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -7800,16 +7803,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C305">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D305">
-        <v>882.50618243</v>
+        <v>885.94077315</v>
       </c>
       <c r="E305">
         <v>785.21813144</v>
       </c>
       <c r="F305">
-        <v>97.28805098999999</v>
+        <v>100.7226417100001</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -7820,16 +7823,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C306">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D306">
-        <v>879.0245291700001</v>
+        <v>882.50618243</v>
       </c>
       <c r="E306">
         <v>785.21813144</v>
       </c>
       <c r="F306">
-        <v>93.80639773000007</v>
+        <v>97.28805098999999</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -7840,16 +7843,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C307">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D307">
-        <v>875.49516449</v>
+        <v>879.0245291700001</v>
       </c>
       <c r="E307">
         <v>785.21813144</v>
       </c>
       <c r="F307">
-        <v>90.27703305</v>
+        <v>93.80639773000007</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -7860,16 +7863,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C308">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D308">
-        <v>871.91748547</v>
+        <v>875.49516449</v>
       </c>
       <c r="E308">
         <v>785.21813144</v>
       </c>
       <c r="F308">
-        <v>86.69935402999999</v>
+        <v>90.27703305</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -7880,16 +7883,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C309">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D309">
-        <v>868.29093497</v>
+        <v>871.91748547</v>
       </c>
       <c r="E309">
         <v>785.21813144</v>
       </c>
       <c r="F309">
-        <v>83.07280352999999</v>
+        <v>86.69935402999999</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -7900,16 +7903,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C310">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D310">
-        <v>864.61500024</v>
+        <v>868.29093497</v>
       </c>
       <c r="E310">
         <v>785.21813144</v>
       </c>
       <c r="F310">
-        <v>79.39686879999999</v>
+        <v>83.07280352999999</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -7920,16 +7923,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C311">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D311">
-        <v>860.8892147</v>
+        <v>864.61500024</v>
       </c>
       <c r="E311">
         <v>785.21813144</v>
       </c>
       <c r="F311">
-        <v>75.67108326000005</v>
+        <v>79.39686879999999</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -7940,16 +7943,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C312">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D312">
-        <v>857.11315544</v>
+        <v>860.8892147</v>
       </c>
       <c r="E312">
         <v>785.21813144</v>
       </c>
       <c r="F312">
-        <v>71.89502400000003</v>
+        <v>75.67108326000005</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -7960,16 +7963,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C313">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D313">
-        <v>853.28644389</v>
+        <v>857.11315544</v>
       </c>
       <c r="E313">
         <v>785.21813144</v>
       </c>
       <c r="F313">
-        <v>68.06831245000001</v>
+        <v>71.89502400000003</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -7980,16 +7983,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C314">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D314">
-        <v>849.40874564</v>
+        <v>853.28644389</v>
       </c>
       <c r="E314">
         <v>785.21813144</v>
       </c>
       <c r="F314">
-        <v>64.19061420000003</v>
+        <v>68.06831245000001</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -8000,16 +8003,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C315">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D315">
-        <v>845.47976976</v>
+        <v>849.40874564</v>
       </c>
       <c r="E315">
         <v>785.21813144</v>
       </c>
       <c r="F315">
-        <v>60.26163831999997</v>
+        <v>64.19061420000003</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -8017,19 +8020,19 @@
         <v>320</v>
       </c>
       <c r="B316">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C316">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D316">
-        <v>913.4923138</v>
+        <v>845.47976976</v>
       </c>
       <c r="E316">
-        <v>820.73950751</v>
+        <v>785.21813144</v>
       </c>
       <c r="F316">
-        <v>92.75280629000008</v>
+        <v>60.26163831999997</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -8040,16 +8043,16 @@
         <v>0.075</v>
       </c>
       <c r="C317">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D317">
-        <v>910.43459397</v>
+        <v>913.4923138</v>
       </c>
       <c r="E317">
-        <v>801.71845773</v>
+        <v>820.73950751</v>
       </c>
       <c r="F317">
-        <v>108.7161362400001</v>
+        <v>92.75280629000008</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -8060,16 +8063,16 @@
         <v>0.075</v>
       </c>
       <c r="C318">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D318">
-        <v>907.33673235</v>
+        <v>910.43459397</v>
       </c>
       <c r="E318">
-        <v>785.21813144</v>
+        <v>801.71845773</v>
       </c>
       <c r="F318">
-        <v>122.1186009100001</v>
+        <v>108.7161362400001</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -8080,16 +8083,16 @@
         <v>0.075</v>
       </c>
       <c r="C319">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D319">
-        <v>904.19765776</v>
+        <v>907.33673235</v>
       </c>
       <c r="E319">
         <v>785.21813144</v>
       </c>
       <c r="F319">
-        <v>118.97952632</v>
+        <v>122.1186009100001</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -8100,16 +8103,16 @@
         <v>0.075</v>
       </c>
       <c r="C320">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D320">
-        <v>901.01634919</v>
+        <v>904.19765776</v>
       </c>
       <c r="E320">
         <v>785.21813144</v>
       </c>
       <c r="F320">
-        <v>115.79821775</v>
+        <v>118.97952632</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -8120,16 +8123,16 @@
         <v>0.075</v>
       </c>
       <c r="C321">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D321">
-        <v>897.79183577</v>
+        <v>901.01634919</v>
       </c>
       <c r="E321">
         <v>785.21813144</v>
       </c>
       <c r="F321">
-        <v>112.5737043300001</v>
+        <v>115.79821775</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -8140,16 +8143,16 @@
         <v>0.075</v>
       </c>
       <c r="C322">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D322">
-        <v>894.52319622</v>
+        <v>897.79183577</v>
       </c>
       <c r="E322">
         <v>785.21813144</v>
       </c>
       <c r="F322">
-        <v>109.3050647800001</v>
+        <v>112.5737043300001</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -8160,16 +8163,16 @@
         <v>0.075</v>
       </c>
       <c r="C323">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D323">
-        <v>891.20955813</v>
+        <v>894.52319622</v>
       </c>
       <c r="E323">
         <v>785.21813144</v>
       </c>
       <c r="F323">
-        <v>105.99142669</v>
+        <v>109.3050647800001</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -8180,16 +8183,16 @@
         <v>0.075</v>
       </c>
       <c r="C324">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D324">
-        <v>887.8500974999999</v>
+        <v>891.20955813</v>
       </c>
       <c r="E324">
         <v>785.21813144</v>
       </c>
       <c r="F324">
-        <v>102.63196606</v>
+        <v>105.99142669</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -8200,16 +8203,16 @@
         <v>0.075</v>
       </c>
       <c r="C325">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D325">
-        <v>884.44403855</v>
+        <v>887.8500974999999</v>
       </c>
       <c r="E325">
         <v>785.21813144</v>
       </c>
       <c r="F325">
-        <v>99.22590710999998</v>
+        <v>102.63196606</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -8220,16 +8223,16 @@
         <v>0.075</v>
       </c>
       <c r="C326">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D326">
-        <v>880.99065291</v>
+        <v>884.44403855</v>
       </c>
       <c r="E326">
         <v>785.21813144</v>
       </c>
       <c r="F326">
-        <v>95.77252147000002</v>
+        <v>99.22590710999998</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -8240,16 +8243,16 @@
         <v>0.075</v>
       </c>
       <c r="C327">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D327">
-        <v>877.48925954</v>
+        <v>880.99065291</v>
       </c>
       <c r="E327">
         <v>785.21813144</v>
       </c>
       <c r="F327">
-        <v>92.27112810000006</v>
+        <v>95.77252147000002</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -8260,16 +8263,16 @@
         <v>0.075</v>
       </c>
       <c r="C328">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D328">
-        <v>873.9392232599999</v>
+        <v>877.48925954</v>
       </c>
       <c r="E328">
         <v>785.21813144</v>
       </c>
       <c r="F328">
-        <v>88.72109181999997</v>
+        <v>92.27112810000006</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -8280,16 +8283,16 @@
         <v>0.075</v>
       </c>
       <c r="C329">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D329">
-        <v>870.33995666</v>
+        <v>873.9392232599999</v>
       </c>
       <c r="E329">
         <v>785.21813144</v>
       </c>
       <c r="F329">
-        <v>85.12182522000001</v>
+        <v>88.72109181999997</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -8300,16 +8303,16 @@
         <v>0.075</v>
       </c>
       <c r="C330">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D330">
-        <v>866.6909171900001</v>
+        <v>870.33995666</v>
       </c>
       <c r="E330">
         <v>785.21813144</v>
       </c>
       <c r="F330">
-        <v>81.47278575000007</v>
+        <v>85.12182522000001</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -8320,16 +8323,16 @@
         <v>0.075</v>
       </c>
       <c r="C331">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D331">
-        <v>862.9916081</v>
+        <v>866.6909171900001</v>
       </c>
       <c r="E331">
         <v>785.21813144</v>
       </c>
       <c r="F331">
-        <v>77.77347666000003</v>
+        <v>81.47278575000007</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -8340,16 +8343,16 @@
         <v>0.075</v>
       </c>
       <c r="C332">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D332">
-        <v>859.2415780600001</v>
+        <v>862.9916081</v>
       </c>
       <c r="E332">
         <v>785.21813144</v>
       </c>
       <c r="F332">
-        <v>74.02344662000007</v>
+        <v>77.77347666000003</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -8360,16 +8363,16 @@
         <v>0.075</v>
       </c>
       <c r="C333">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D333">
-        <v>855.44042043</v>
+        <v>859.2415780600001</v>
       </c>
       <c r="E333">
         <v>785.21813144</v>
       </c>
       <c r="F333">
-        <v>70.22228899000004</v>
+        <v>74.02344662000007</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -8380,16 +8383,16 @@
         <v>0.075</v>
       </c>
       <c r="C334">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D334">
-        <v>851.58777329</v>
+        <v>855.44042043</v>
       </c>
       <c r="E334">
         <v>785.21813144</v>
       </c>
       <c r="F334">
-        <v>66.36964184999999</v>
+        <v>70.22228899000004</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -8400,16 +8403,16 @@
         <v>0.075</v>
       </c>
       <c r="C335">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D335">
-        <v>847.68331893</v>
+        <v>851.58777329</v>
       </c>
       <c r="E335">
         <v>785.21813144</v>
       </c>
       <c r="F335">
-        <v>62.46518749000006</v>
+        <v>66.36964184999999</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -8420,16 +8423,16 @@
         <v>0.075</v>
       </c>
       <c r="C336">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D336">
-        <v>843.72678375</v>
+        <v>847.68331893</v>
       </c>
       <c r="E336">
         <v>785.21813144</v>
       </c>
       <c r="F336">
-        <v>58.50865231</v>
+        <v>62.46518749000006</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -8437,19 +8440,19 @@
         <v>341</v>
       </c>
       <c r="B337">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="C337">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D337">
-        <v>912.11263823</v>
+        <v>843.72678375</v>
       </c>
       <c r="E337">
-        <v>820.73950751</v>
+        <v>785.21813144</v>
       </c>
       <c r="F337">
-        <v>91.37313072000006</v>
+        <v>58.50865231</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -8460,16 +8463,16 @@
         <v>0.08</v>
       </c>
       <c r="C338">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D338">
-        <v>909.0450067100001</v>
+        <v>912.11263823</v>
       </c>
       <c r="E338">
-        <v>801.51456094</v>
+        <v>820.73950751</v>
       </c>
       <c r="F338">
-        <v>107.53044577</v>
+        <v>91.37313072000006</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -8480,16 +8483,16 @@
         <v>0.08</v>
       </c>
       <c r="C339">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D339">
-        <v>905.93615665</v>
+        <v>909.0450067100001</v>
       </c>
       <c r="E339">
-        <v>785.21813144</v>
+        <v>801.51456094</v>
       </c>
       <c r="F339">
-        <v>120.7180252100001</v>
+        <v>107.53044577</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -8500,16 +8503,16 @@
         <v>0.08</v>
       </c>
       <c r="C340">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D340">
-        <v>902.7850294900001</v>
+        <v>905.93615665</v>
       </c>
       <c r="E340">
         <v>785.21813144</v>
       </c>
       <c r="F340">
-        <v>117.5668980500001</v>
+        <v>120.7180252100001</v>
       </c>
     </row>
     <row r="341" spans="1:6">
@@ -8520,16 +8523,16 @@
         <v>0.08</v>
       </c>
       <c r="C341">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D341">
-        <v>899.59061608</v>
+        <v>902.7850294900001</v>
       </c>
       <c r="E341">
         <v>785.21813144</v>
       </c>
       <c r="F341">
-        <v>114.37248464</v>
+        <v>117.5668980500001</v>
       </c>
     </row>
     <row r="342" spans="1:6">
@@ -8540,16 +8543,16 @@
         <v>0.08</v>
       </c>
       <c r="C342">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D342">
-        <v>896.35195771</v>
+        <v>899.59061608</v>
       </c>
       <c r="E342">
         <v>785.21813144</v>
       </c>
       <c r="F342">
-        <v>111.13382627</v>
+        <v>114.37248464</v>
       </c>
     </row>
     <row r="343" spans="1:6">
@@ -8560,16 +8563,16 @@
         <v>0.08</v>
       </c>
       <c r="C343">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D343">
-        <v>893.06814564</v>
+        <v>896.35195771</v>
       </c>
       <c r="E343">
         <v>785.21813144</v>
       </c>
       <c r="F343">
-        <v>107.8500142</v>
+        <v>111.13382627</v>
       </c>
     </row>
     <row r="344" spans="1:6">
@@ -8580,16 +8583,16 @@
         <v>0.08</v>
       </c>
       <c r="C344">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D344">
-        <v>889.73832047</v>
+        <v>893.06814564</v>
       </c>
       <c r="E344">
         <v>785.21813144</v>
       </c>
       <c r="F344">
-        <v>104.52018903</v>
+        <v>107.8500142</v>
       </c>
     </row>
     <row r="345" spans="1:6">
@@ -8600,16 +8603,16 @@
         <v>0.08</v>
       </c>
       <c r="C345">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D345">
-        <v>886.36167185</v>
+        <v>889.73832047</v>
       </c>
       <c r="E345">
         <v>785.21813144</v>
       </c>
       <c r="F345">
-        <v>101.14354041</v>
+        <v>104.52018903</v>
       </c>
     </row>
     <row r="346" spans="1:6">
@@ -8620,16 +8623,16 @@
         <v>0.08</v>
       </c>
       <c r="C346">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D346">
-        <v>882.93743719</v>
+        <v>886.36167185</v>
       </c>
       <c r="E346">
         <v>785.21813144</v>
       </c>
       <c r="F346">
-        <v>97.71930574999999</v>
+        <v>101.14354041</v>
       </c>
     </row>
     <row r="347" spans="1:6">
@@ -8640,16 +8643,16 @@
         <v>0.08</v>
       </c>
       <c r="C347">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D347">
-        <v>879.46490269</v>
+        <v>882.93743719</v>
       </c>
       <c r="E347">
         <v>785.21813144</v>
       </c>
       <c r="F347">
-        <v>94.24677125000005</v>
+        <v>97.71930574999999</v>
       </c>
     </row>
     <row r="348" spans="1:6">
@@ -8660,16 +8663,16 @@
         <v>0.08</v>
       </c>
       <c r="C348">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D348">
-        <v>875.94340152</v>
+        <v>879.46490269</v>
       </c>
       <c r="E348">
         <v>785.21813144</v>
       </c>
       <c r="F348">
-        <v>90.72527007999997</v>
+        <v>94.24677125000005</v>
       </c>
     </row>
     <row r="349" spans="1:6">
@@ -8680,16 +8683,16 @@
         <v>0.08</v>
       </c>
       <c r="C349">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D349">
-        <v>872.37231385</v>
+        <v>875.94340152</v>
       </c>
       <c r="E349">
         <v>785.21813144</v>
       </c>
       <c r="F349">
-        <v>87.15418240999998</v>
+        <v>90.72527007999997</v>
       </c>
     </row>
     <row r="350" spans="1:6">
@@ -8700,16 +8703,16 @@
         <v>0.08</v>
       </c>
       <c r="C350">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D350">
-        <v>868.75106676</v>
+        <v>872.37231385</v>
       </c>
       <c r="E350">
         <v>785.21813144</v>
       </c>
       <c r="F350">
-        <v>83.53293531999998</v>
+        <v>87.15418240999998</v>
       </c>
     </row>
     <row r="351" spans="1:6">
@@ -8720,16 +8723,16 @@
         <v>0.08</v>
       </c>
       <c r="C351">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D351">
-        <v>865.07913353</v>
+        <v>868.75106676</v>
       </c>
       <c r="E351">
         <v>785.21813144</v>
       </c>
       <c r="F351">
-        <v>79.86100209000006</v>
+        <v>83.53293531999998</v>
       </c>
     </row>
     <row r="352" spans="1:6">
@@ -8740,16 +8743,16 @@
         <v>0.08</v>
       </c>
       <c r="C352">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D352">
-        <v>861.3560333299999</v>
+        <v>865.07913353</v>
       </c>
       <c r="E352">
         <v>785.21813144</v>
       </c>
       <c r="F352">
-        <v>76.13790188999997</v>
+        <v>79.86100209000006</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -8760,16 +8763,16 @@
         <v>0.08</v>
       </c>
       <c r="C353">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D353">
-        <v>857.5813309500001</v>
+        <v>861.3560333299999</v>
       </c>
       <c r="E353">
         <v>785.21813144</v>
       </c>
       <c r="F353">
-        <v>72.36319951000007</v>
+        <v>76.13790188999997</v>
       </c>
     </row>
     <row r="354" spans="1:6">
@@ -8780,16 +8783,16 @@
         <v>0.08</v>
       </c>
       <c r="C354">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D354">
-        <v>853.75463625</v>
+        <v>857.5813309500001</v>
       </c>
       <c r="E354">
         <v>785.21813144</v>
       </c>
       <c r="F354">
-        <v>68.53650481</v>
+        <v>72.36319951000007</v>
       </c>
     </row>
     <row r="355" spans="1:6">
@@ -8800,16 +8803,16 @@
         <v>0.08</v>
       </c>
       <c r="C355">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D355">
-        <v>849.8756044</v>
+        <v>853.75463625</v>
       </c>
       <c r="E355">
         <v>785.21813144</v>
       </c>
       <c r="F355">
-        <v>64.65747296000006</v>
+        <v>68.53650481</v>
       </c>
     </row>
     <row r="356" spans="1:6">
@@ -8820,16 +8823,16 @@
         <v>0.08</v>
       </c>
       <c r="C356">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D356">
-        <v>845.94393502</v>
+        <v>849.8756044</v>
       </c>
       <c r="E356">
         <v>785.21813144</v>
       </c>
       <c r="F356">
-        <v>60.72580358000005</v>
+        <v>64.65747296000006</v>
       </c>
     </row>
     <row r="357" spans="1:6">
@@ -8840,16 +8843,16 @@
         <v>0.08</v>
       </c>
       <c r="C357">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D357">
-        <v>841.9593721</v>
+        <v>845.94393502</v>
       </c>
       <c r="E357">
         <v>785.21813144</v>
       </c>
       <c r="F357">
-        <v>56.74124066000002</v>
+        <v>60.72580358000005</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -8857,19 +8860,19 @@
         <v>362</v>
       </c>
       <c r="B358">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="C358">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D358">
-        <v>910.7252549</v>
+        <v>841.9593721</v>
       </c>
       <c r="E358">
-        <v>820.73950751</v>
+        <v>785.21813144</v>
       </c>
       <c r="F358">
-        <v>89.98574739000003</v>
+        <v>56.74124066000002</v>
       </c>
     </row>
     <row r="359" spans="1:6">
@@ -8880,16 +8883,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C359">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D359">
-        <v>907.64749466</v>
+        <v>910.7252549</v>
       </c>
       <c r="E359">
-        <v>801.30624708</v>
+        <v>820.73950751</v>
       </c>
       <c r="F359">
-        <v>106.34124758</v>
+        <v>89.98574739000003</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -8900,16 +8903,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C360">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D360">
-        <v>904.52742335</v>
+        <v>907.64749466</v>
       </c>
       <c r="E360">
-        <v>785.21813144</v>
+        <v>801.30624708</v>
       </c>
       <c r="F360">
-        <v>119.3092919100001</v>
+        <v>106.34124758</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -8920,16 +8923,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C361">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D361">
-        <v>901.36399276</v>
+        <v>904.52742335</v>
       </c>
       <c r="E361">
         <v>785.21813144</v>
       </c>
       <c r="F361">
-        <v>116.14586132</v>
+        <v>119.3092919100001</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -8940,16 +8943,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C362">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D362">
-        <v>898.15620632</v>
+        <v>901.36399276</v>
       </c>
       <c r="E362">
         <v>785.21813144</v>
       </c>
       <c r="F362">
-        <v>112.93807488</v>
+        <v>116.14586132</v>
       </c>
     </row>
     <row r="363" spans="1:6">
@@ -8960,16 +8963,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C363">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D363">
-        <v>894.90311829</v>
+        <v>898.15620632</v>
       </c>
       <c r="E363">
         <v>785.21813144</v>
       </c>
       <c r="F363">
-        <v>109.68498685</v>
+        <v>112.93807488</v>
       </c>
     </row>
     <row r="364" spans="1:6">
@@ -8980,16 +8983,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C364">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D364">
-        <v>891.6038330600001</v>
+        <v>894.90311829</v>
       </c>
       <c r="E364">
         <v>785.21813144</v>
       </c>
       <c r="F364">
-        <v>106.3857016200001</v>
+        <v>109.68498685</v>
       </c>
     </row>
     <row r="365" spans="1:6">
@@ -9000,16 +9003,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C365">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D365">
-        <v>888.25750469</v>
+        <v>891.6038330600001</v>
       </c>
       <c r="E365">
         <v>785.21813144</v>
       </c>
       <c r="F365">
-        <v>103.03937325</v>
+        <v>106.3857016200001</v>
       </c>
     </row>
     <row r="366" spans="1:6">
@@ -9020,16 +9023,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C366">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D366">
-        <v>884.8633366400001</v>
+        <v>888.25750469</v>
       </c>
       <c r="E366">
         <v>785.21813144</v>
       </c>
       <c r="F366">
-        <v>99.64520520000008</v>
+        <v>103.03937325</v>
       </c>
     </row>
     <row r="367" spans="1:6">
@@ -9040,16 +9043,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C367">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D367">
-        <v>881.4205809</v>
+        <v>884.8633366400001</v>
       </c>
       <c r="E367">
         <v>785.21813144</v>
       </c>
       <c r="F367">
-        <v>96.20244946000003</v>
+        <v>99.64520520000008</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -9060,16 +9063,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C368">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D368">
-        <v>877.92853825</v>
+        <v>881.4205809</v>
       </c>
       <c r="E368">
         <v>785.21813144</v>
       </c>
       <c r="F368">
-        <v>92.71040680999999</v>
+        <v>96.20244946000003</v>
       </c>
     </row>
     <row r="369" spans="1:6">
@@ -9080,16 +9083,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C369">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D369">
-        <v>874.38655566</v>
+        <v>877.92853825</v>
       </c>
       <c r="E369">
         <v>785.21813144</v>
       </c>
       <c r="F369">
-        <v>89.16842422000002</v>
+        <v>92.71040680999999</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -9100,16 +9103,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C370">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D370">
-        <v>870.79402996</v>
+        <v>874.38655566</v>
       </c>
       <c r="E370">
         <v>785.21813144</v>
       </c>
       <c r="F370">
-        <v>85.57589852000001</v>
+        <v>89.16842422000002</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -9120,16 +9123,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C371">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D371">
-        <v>867.15040335</v>
+        <v>870.79402996</v>
       </c>
       <c r="E371">
         <v>785.21813144</v>
       </c>
       <c r="F371">
-        <v>81.93227191000005</v>
+        <v>85.57589852000001</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -9140,16 +9143,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C372">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D372">
-        <v>863.45516488</v>
+        <v>867.15040335</v>
       </c>
       <c r="E372">
         <v>785.21813144</v>
       </c>
       <c r="F372">
-        <v>78.23703344</v>
+        <v>81.93227191000005</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -9160,16 +9163,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C373">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D373">
-        <v>859.70785028</v>
+        <v>863.45516488</v>
       </c>
       <c r="E373">
         <v>785.21813144</v>
       </c>
       <c r="F373">
-        <v>74.48971884000002</v>
+        <v>78.23703344</v>
       </c>
     </row>
     <row r="374" spans="1:6">
@@ -9180,16 +9183,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C374">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D374">
-        <v>855.90804096</v>
+        <v>859.70785028</v>
       </c>
       <c r="E374">
         <v>785.21813144</v>
       </c>
       <c r="F374">
-        <v>70.68990952000001</v>
+        <v>74.48971884000002</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -9200,16 +9203,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C375">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D375">
-        <v>852.0553639</v>
+        <v>855.90804096</v>
       </c>
       <c r="E375">
         <v>785.21813144</v>
       </c>
       <c r="F375">
-        <v>66.83723246</v>
+        <v>70.68990952000001</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -9220,16 +9223,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C376">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D376">
-        <v>848.14949156</v>
+        <v>852.0553639</v>
       </c>
       <c r="E376">
         <v>785.21813144</v>
       </c>
       <c r="F376">
-        <v>62.93136012000002</v>
+        <v>66.83723246</v>
       </c>
     </row>
     <row r="377" spans="1:6">
@@ -9240,16 +9243,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C377">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D377">
-        <v>844.19014121</v>
+        <v>848.14949156</v>
       </c>
       <c r="E377">
         <v>785.21813144</v>
       </c>
       <c r="F377">
-        <v>58.97200977</v>
+        <v>62.93136012000002</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -9260,16 +9263,16 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="C378">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D378">
-        <v>840.17707522</v>
+        <v>844.19014121</v>
       </c>
       <c r="E378">
         <v>785.21813144</v>
       </c>
       <c r="F378">
-        <v>54.95894378000003</v>
+        <v>58.97200977</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -9277,19 +9280,19 @@
         <v>383</v>
       </c>
       <c r="B379">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C379">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D379">
-        <v>909.32980857</v>
+        <v>840.17707522</v>
       </c>
       <c r="E379">
-        <v>820.73950751</v>
+        <v>785.21813144</v>
       </c>
       <c r="F379">
-        <v>88.59030106</v>
+        <v>54.95894378000003</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -9300,16 +9303,16 @@
         <v>0.09</v>
       </c>
       <c r="C380">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D380">
-        <v>906.24170053</v>
+        <v>909.32980857</v>
       </c>
       <c r="E380">
-        <v>801.0933711599999</v>
+        <v>820.73950751</v>
       </c>
       <c r="F380">
-        <v>105.1483293700001</v>
+        <v>88.59030106</v>
       </c>
     </row>
     <row r="381" spans="1:6">
@@ -9320,16 +9323,16 @@
         <v>0.09</v>
       </c>
       <c r="C381">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D381">
-        <v>903.11016927</v>
+        <v>906.24170053</v>
       </c>
       <c r="E381">
-        <v>785.21813144</v>
+        <v>801.0933711599999</v>
       </c>
       <c r="F381">
-        <v>117.89203783</v>
+        <v>105.1483293700001</v>
       </c>
     </row>
     <row r="382" spans="1:6">
@@ -9340,16 +9343,16 @@
         <v>0.09</v>
       </c>
       <c r="C382">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D382">
-        <v>899.93417922</v>
+        <v>903.11016927</v>
       </c>
       <c r="E382">
         <v>785.21813144</v>
       </c>
       <c r="F382">
-        <v>114.7160477800001</v>
+        <v>117.89203783</v>
       </c>
     </row>
     <row r="383" spans="1:6">
@@ -9360,16 +9363,16 @@
         <v>0.09</v>
       </c>
       <c r="C383">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D383">
-        <v>896.71274678</v>
+        <v>899.93417922</v>
       </c>
       <c r="E383">
         <v>785.21813144</v>
       </c>
       <c r="F383">
-        <v>111.49461534</v>
+        <v>114.7160477800001</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -9380,16 +9383,16 @@
         <v>0.09</v>
       </c>
       <c r="C384">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D384">
-        <v>893.44493937</v>
+        <v>896.71274678</v>
       </c>
       <c r="E384">
         <v>785.21813144</v>
       </c>
       <c r="F384">
-        <v>108.2268079300001</v>
+        <v>111.49461534</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -9400,16 +9403,16 @@
         <v>0.09</v>
       </c>
       <c r="C385">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D385">
-        <v>890.12987509</v>
+        <v>893.44493937</v>
       </c>
       <c r="E385">
         <v>785.21813144</v>
       </c>
       <c r="F385">
-        <v>104.9117436500001</v>
+        <v>108.2268079300001</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -9420,16 +9423,16 @@
         <v>0.09</v>
       </c>
       <c r="C386">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D386">
-        <v>886.76672192</v>
+        <v>890.12987509</v>
       </c>
       <c r="E386">
         <v>785.21813144</v>
       </c>
       <c r="F386">
-        <v>101.54859048</v>
+        <v>104.9117436500001</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -9440,16 +9443,16 @@
         <v>0.09</v>
       </c>
       <c r="C387">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D387">
-        <v>883.35469778</v>
+        <v>886.76672192</v>
       </c>
       <c r="E387">
         <v>785.21813144</v>
       </c>
       <c r="F387">
-        <v>98.13656634000006</v>
+        <v>101.54859048</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -9460,16 +9463,16 @@
         <v>0.09</v>
       </c>
       <c r="C388">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D388">
-        <v>879.89306934</v>
+        <v>883.35469778</v>
       </c>
       <c r="E388">
         <v>785.21813144</v>
       </c>
       <c r="F388">
-        <v>94.67493790000003</v>
+        <v>98.13656634000006</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -9480,16 +9483,16 @@
         <v>0.09</v>
       </c>
       <c r="C389">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D389">
-        <v>876.38115206</v>
+        <v>879.89306934</v>
       </c>
       <c r="E389">
         <v>785.21813144</v>
       </c>
       <c r="F389">
-        <v>91.16302062</v>
+        <v>94.67493790000003</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -9500,16 +9503,16 @@
         <v>0.09</v>
       </c>
       <c r="C390">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D390">
-        <v>872.8183095000001</v>
+        <v>876.38115206</v>
       </c>
       <c r="E390">
         <v>785.21813144</v>
       </c>
       <c r="F390">
-        <v>87.60017806000008</v>
+        <v>91.16302062</v>
       </c>
     </row>
     <row r="391" spans="1:6">
@@ -9520,16 +9523,16 @@
         <v>0.09</v>
       </c>
       <c r="C391">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D391">
-        <v>869.20395301</v>
+        <v>872.8183095000001</v>
       </c>
       <c r="E391">
         <v>785.21813144</v>
       </c>
       <c r="F391">
-        <v>83.98582156999998</v>
+        <v>87.60017806000008</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -9540,16 +9543,16 @@
         <v>0.09</v>
       </c>
       <c r="C392">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D392">
-        <v>865.5375411700001</v>
+        <v>869.20395301</v>
       </c>
       <c r="E392">
         <v>785.21813144</v>
       </c>
       <c r="F392">
-        <v>80.31940973000007</v>
+        <v>83.98582156999998</v>
       </c>
     </row>
     <row r="393" spans="1:6">
@@ -9560,16 +9563,16 @@
         <v>0.09</v>
       </c>
       <c r="C393">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D393">
-        <v>861.81857976</v>
+        <v>865.5375411700001</v>
       </c>
       <c r="E393">
         <v>785.21813144</v>
       </c>
       <c r="F393">
-        <v>76.60044832000005</v>
+        <v>80.31940973000007</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -9580,16 +9583,16 @@
         <v>0.09</v>
       </c>
       <c r="C394">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D394">
-        <v>858.04662101</v>
+        <v>861.81857976</v>
       </c>
       <c r="E394">
         <v>785.21813144</v>
       </c>
       <c r="F394">
-        <v>72.82848956999999</v>
+        <v>76.60044832000005</v>
       </c>
     </row>
     <row r="395" spans="1:6">
@@ -9600,16 +9603,16 @@
         <v>0.09</v>
       </c>
       <c r="C395">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D395">
-        <v>854.22126354</v>
+        <v>858.04662101</v>
       </c>
       <c r="E395">
         <v>785.21813144</v>
       </c>
       <c r="F395">
-        <v>69.00313210000002</v>
+        <v>72.82848956999999</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -9620,16 +9623,16 @@
         <v>0.09</v>
       </c>
       <c r="C396">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D396">
-        <v>850.3421519</v>
+        <v>854.22126354</v>
       </c>
       <c r="E396">
         <v>785.21813144</v>
       </c>
       <c r="F396">
-        <v>65.12402046</v>
+        <v>69.00313210000002</v>
       </c>
     </row>
     <row r="397" spans="1:6">
@@ -9640,16 +9643,16 @@
         <v>0.09</v>
       </c>
       <c r="C397">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D397">
-        <v>846.40897626</v>
+        <v>850.3421519</v>
       </c>
       <c r="E397">
         <v>785.21813144</v>
       </c>
       <c r="F397">
-        <v>61.19084482000005</v>
+        <v>65.12402046</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -9660,16 +9663,16 @@
         <v>0.09</v>
       </c>
       <c r="C398">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D398">
-        <v>842.42147231</v>
+        <v>846.40897626</v>
       </c>
       <c r="E398">
         <v>785.21813144</v>
       </c>
       <c r="F398">
-        <v>57.20334087000003</v>
+        <v>61.19084482000005</v>
       </c>
     </row>
     <row r="399" spans="1:6">
@@ -9680,16 +9683,16 @@
         <v>0.09</v>
       </c>
       <c r="C399">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D399">
-        <v>838.37942085</v>
+        <v>842.42147231</v>
       </c>
       <c r="E399">
         <v>785.21813144</v>
       </c>
       <c r="F399">
-        <v>53.16128940999999</v>
+        <v>57.20334087000003</v>
       </c>
     </row>
     <row r="400" spans="1:6">
@@ -9697,19 +9700,19 @@
         <v>404</v>
       </c>
       <c r="B400">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="C400">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D400">
-        <v>907.92593211</v>
+        <v>838.37942085</v>
       </c>
       <c r="E400">
-        <v>820.73950727</v>
+        <v>785.21813144</v>
       </c>
       <c r="F400">
-        <v>87.18642483999997</v>
+        <v>53.16128940999999</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -9720,16 +9723,16 @@
         <v>0.095</v>
       </c>
       <c r="C401">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D401">
-        <v>904.82725223</v>
+        <v>907.92593211</v>
       </c>
       <c r="E401">
-        <v>800.87578177</v>
+        <v>820.73950727</v>
       </c>
       <c r="F401">
-        <v>103.95147046</v>
+        <v>87.18642483999997</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -9740,16 +9743,16 @@
         <v>0.095</v>
       </c>
       <c r="C402">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D402">
-        <v>901.68401856</v>
+        <v>904.82725223</v>
       </c>
       <c r="E402">
-        <v>785.21813144</v>
+        <v>800.87578177</v>
       </c>
       <c r="F402">
-        <v>116.46588712</v>
+        <v>103.95147046</v>
       </c>
     </row>
     <row r="403" spans="1:6">
@@ -9760,16 +9763,16 @@
         <v>0.095</v>
       </c>
       <c r="C403">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D403">
-        <v>898.4952085899999</v>
+        <v>901.68401856</v>
       </c>
       <c r="E403">
         <v>785.21813144</v>
       </c>
       <c r="F403">
-        <v>113.27707715</v>
+        <v>116.46588712</v>
       </c>
     </row>
     <row r="404" spans="1:6">
@@ -9780,16 +9783,16 @@
         <v>0.095</v>
       </c>
       <c r="C404">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D404">
-        <v>895.25985227</v>
+        <v>898.4952085899999</v>
       </c>
       <c r="E404">
         <v>785.21813144</v>
       </c>
       <c r="F404">
-        <v>110.04172083</v>
+        <v>113.27707715</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -9800,16 +9803,16 @@
         <v>0.095</v>
       </c>
       <c r="C405">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D405">
-        <v>891.97703059</v>
+        <v>895.25985227</v>
       </c>
       <c r="E405">
         <v>785.21813144</v>
       </c>
       <c r="F405">
-        <v>106.75889915</v>
+        <v>110.04172083</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -9820,16 +9823,16 @@
         <v>0.095</v>
       </c>
       <c r="C406">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D406">
-        <v>888.64587596</v>
+        <v>891.97703059</v>
       </c>
       <c r="E406">
         <v>785.21813144</v>
       </c>
       <c r="F406">
-        <v>103.42774452</v>
+        <v>106.75889915</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -9840,16 +9843,16 @@
         <v>0.095</v>
       </c>
       <c r="C407">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D407">
-        <v>885.2655710400001</v>
+        <v>888.64587596</v>
       </c>
       <c r="E407">
         <v>785.21813144</v>
       </c>
       <c r="F407">
-        <v>100.0474396000001</v>
+        <v>103.42774452</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -9860,16 +9863,16 @@
         <v>0.095</v>
       </c>
       <c r="C408">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D408">
-        <v>881.8353484</v>
+        <v>885.2655710400001</v>
       </c>
       <c r="E408">
         <v>785.21813144</v>
       </c>
       <c r="F408">
-        <v>96.61721696000006</v>
+        <v>100.0474396000001</v>
       </c>
     </row>
     <row r="409" spans="1:6">
@@ -9880,16 +9883,16 @@
         <v>0.095</v>
       </c>
       <c r="C409">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D409">
-        <v>878.3544901499999</v>
+        <v>881.8353484</v>
       </c>
       <c r="E409">
         <v>785.21813144</v>
       </c>
       <c r="F409">
-        <v>93.13635870999997</v>
+        <v>96.61721696000006</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -9900,16 +9903,16 @@
         <v>0.095</v>
       </c>
       <c r="C410">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D410">
-        <v>874.82232675</v>
+        <v>878.3544901499999</v>
       </c>
       <c r="E410">
         <v>785.21813144</v>
       </c>
       <c r="F410">
-        <v>89.60419531000002</v>
+        <v>93.13635870999997</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -9920,16 +9923,16 @@
         <v>0.095</v>
       </c>
       <c r="C411">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D411">
-        <v>871.23823824</v>
+        <v>874.82232675</v>
       </c>
       <c r="E411">
         <v>785.21813144</v>
       </c>
       <c r="F411">
-        <v>86.02010680000001</v>
+        <v>89.60419531000002</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -9940,16 +9943,16 @@
         <v>0.095</v>
       </c>
       <c r="C412">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D412">
-        <v>867.60165202</v>
+        <v>871.23823824</v>
       </c>
       <c r="E412">
         <v>785.21813144</v>
       </c>
       <c r="F412">
-        <v>82.38352057999998</v>
+        <v>86.02010680000001</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -9960,16 +9963,16 @@
         <v>0.095</v>
       </c>
       <c r="C413">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D413">
-        <v>863.91204298</v>
+        <v>867.60165202</v>
       </c>
       <c r="E413">
         <v>785.21813144</v>
       </c>
       <c r="F413">
-        <v>78.69391154000004</v>
+        <v>82.38352057999998</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -9980,16 +9983,16 @@
         <v>0.095</v>
       </c>
       <c r="C414">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D414">
-        <v>860.16893416</v>
+        <v>863.91204298</v>
       </c>
       <c r="E414">
         <v>785.21813144</v>
       </c>
       <c r="F414">
-        <v>74.95080272000007</v>
+        <v>78.69391154000004</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -10000,16 +10003,16 @@
         <v>0.095</v>
       </c>
       <c r="C415">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D415">
-        <v>856.37189481</v>
+        <v>860.16893416</v>
       </c>
       <c r="E415">
         <v>785.21813144</v>
       </c>
       <c r="F415">
-        <v>71.15376336999998</v>
+        <v>74.95080272000007</v>
       </c>
     </row>
     <row r="416" spans="1:6">
@@ -10020,16 +10023,16 @@
         <v>0.095</v>
       </c>
       <c r="C416">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D416">
-        <v>852.52054128</v>
+        <v>856.37189481</v>
       </c>
       <c r="E416">
         <v>785.21813144</v>
       </c>
       <c r="F416">
-        <v>67.30240984</v>
+        <v>71.15376336999998</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -10040,16 +10043,16 @@
         <v>0.095</v>
       </c>
       <c r="C417">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D417">
-        <v>848.61453597</v>
+        <v>852.52054128</v>
       </c>
       <c r="E417">
         <v>785.21813144</v>
       </c>
       <c r="F417">
-        <v>63.39640453000004</v>
+        <v>67.30240984</v>
       </c>
     </row>
     <row r="418" spans="1:6">
@@ -10060,16 +10063,16 @@
         <v>0.095</v>
       </c>
       <c r="C418">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D418">
-        <v>844.65358752</v>
+        <v>848.61453597</v>
       </c>
       <c r="E418">
         <v>785.21813144</v>
       </c>
       <c r="F418">
-        <v>59.43545607999999</v>
+        <v>63.39640453000004</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -10080,16 +10083,16 @@
         <v>0.095</v>
       </c>
       <c r="C419">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D419">
-        <v>840.63745027</v>
+        <v>844.65358752</v>
       </c>
       <c r="E419">
         <v>785.21813144</v>
       </c>
       <c r="F419">
-        <v>55.41931883000007</v>
+        <v>59.43545607999999</v>
       </c>
     </row>
     <row r="420" spans="1:6">
@@ -10100,16 +10103,16 @@
         <v>0.095</v>
       </c>
       <c r="C420">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="D420">
-        <v>836.56592405</v>
+        <v>840.63745027</v>
       </c>
       <c r="E420">
         <v>785.21813144</v>
       </c>
       <c r="F420">
-        <v>51.34779261000006</v>
+        <v>55.41931883000007</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -10117,19 +10120,19 @@
         <v>425</v>
       </c>
       <c r="B421">
+        <v>0.095</v>
+      </c>
+      <c r="C421">
         <v>0.1</v>
       </c>
-      <c r="C421">
-        <v>0</v>
-      </c>
       <c r="D421">
-        <v>906.51324579</v>
+        <v>836.56592405</v>
       </c>
       <c r="E421">
-        <v>820.73950751</v>
+        <v>785.21813144</v>
       </c>
       <c r="F421">
-        <v>85.77373828000009</v>
+        <v>51.34779261000006</v>
       </c>
     </row>
     <row r="422" spans="1:6">
@@ -10140,16 +10143,16 @@
         <v>0.1</v>
       </c>
       <c r="C422">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D422">
-        <v>903.4037660400001</v>
+        <v>906.51324579</v>
       </c>
       <c r="E422">
-        <v>800.65332075</v>
+        <v>820.73950751</v>
       </c>
       <c r="F422">
-        <v>102.75044529</v>
+        <v>85.77373828000009</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -10160,16 +10163,16 @@
         <v>0.1</v>
       </c>
       <c r="C423">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="D423">
-        <v>900.2485830000001</v>
+        <v>903.4037660400001</v>
       </c>
       <c r="E423">
-        <v>785.21813144</v>
+        <v>800.65332075</v>
       </c>
       <c r="F423">
-        <v>115.0304515600001</v>
+        <v>102.75044529</v>
       </c>
     </row>
     <row r="424" spans="1:6">
@@ -10180,16 +10183,16 @@
         <v>0.1</v>
       </c>
       <c r="C424">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D424">
-        <v>897.04668774</v>
+        <v>900.2485830000001</v>
       </c>
       <c r="E424">
         <v>785.21813144</v>
       </c>
       <c r="F424">
-        <v>111.8285563000001</v>
+        <v>115.0304515600001</v>
       </c>
     </row>
     <row r="425" spans="1:6">
@@ -10200,16 +10203,16 @@
         <v>0.1</v>
       </c>
       <c r="C425">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D425">
-        <v>893.79712482</v>
+        <v>897.04668774</v>
       </c>
       <c r="E425">
         <v>785.21813144</v>
       </c>
       <c r="F425">
-        <v>108.57899338</v>
+        <v>111.8285563000001</v>
       </c>
     </row>
     <row r="426" spans="1:6">
@@ -10220,16 +10223,16 @@
         <v>0.1</v>
       </c>
       <c r="C426">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="D426">
-        <v>890.4989891</v>
+        <v>893.79712482</v>
       </c>
       <c r="E426">
         <v>785.21813144</v>
       </c>
       <c r="F426">
-        <v>105.28085766</v>
+        <v>108.57899338</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -10240,16 +10243,16 @@
         <v>0.1</v>
       </c>
       <c r="C427">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="D427">
-        <v>887.15142765</v>
+        <v>890.4989891</v>
       </c>
       <c r="E427">
         <v>785.21813144</v>
       </c>
       <c r="F427">
-        <v>101.93329621</v>
+        <v>105.28085766</v>
       </c>
     </row>
     <row r="428" spans="1:6">
@@ -10260,16 +10263,16 @@
         <v>0.1</v>
       </c>
       <c r="C428">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="D428">
-        <v>883.7536383299999</v>
+        <v>887.15142765</v>
       </c>
       <c r="E428">
         <v>785.21813144</v>
       </c>
       <c r="F428">
-        <v>98.53550688999997</v>
+        <v>101.93329621</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -10280,16 +10283,16 @@
         <v>0.1</v>
       </c>
       <c r="C429">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="D429">
-        <v>880.30486907</v>
+        <v>883.7536383299999</v>
       </c>
       <c r="E429">
         <v>785.21813144</v>
       </c>
       <c r="F429">
-        <v>95.08673763000002</v>
+        <v>98.53550688999997</v>
       </c>
     </row>
     <row r="430" spans="1:6">
@@ -10300,16 +10303,16 @@
         <v>0.1</v>
       </c>
       <c r="C430">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="D430">
-        <v>876.8044174299999</v>
+        <v>880.30486907</v>
       </c>
       <c r="E430">
         <v>785.21813144</v>
       </c>
       <c r="F430">
-        <v>91.58628598999996</v>
+        <v>95.08673763000002</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -10320,16 +10323,16 @@
         <v>0.1</v>
       </c>
       <c r="C431">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="D431">
-        <v>873.25163059</v>
+        <v>876.8044174299999</v>
       </c>
       <c r="E431">
         <v>785.21813144</v>
       </c>
       <c r="F431">
-        <v>88.03349915000001</v>
+        <v>91.58628598999996</v>
       </c>
     </row>
     <row r="432" spans="1:6">
@@ -10340,16 +10343,16 @@
         <v>0.1</v>
       </c>
       <c r="C432">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="D432">
-        <v>869.64590426</v>
+        <v>873.25163059</v>
       </c>
       <c r="E432">
         <v>785.21813144</v>
       </c>
       <c r="F432">
-        <v>84.42777281999997</v>
+        <v>88.03349915000001</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -10360,16 +10363,16 @@
         <v>0.1</v>
       </c>
       <c r="C433">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="D433">
-        <v>865.98668281</v>
+        <v>869.64590426</v>
       </c>
       <c r="E433">
         <v>785.21813144</v>
       </c>
       <c r="F433">
-        <v>80.76855137000007</v>
+        <v>84.42777281999997</v>
       </c>
     </row>
     <row r="434" spans="1:6">
@@ -10380,16 +10383,16 @@
         <v>0.1</v>
       </c>
       <c r="C434">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="D434">
-        <v>862.27345843</v>
+        <v>865.98668281</v>
       </c>
       <c r="E434">
         <v>785.21813144</v>
       </c>
       <c r="F434">
-        <v>77.05532699000003</v>
+        <v>80.76855137000007</v>
       </c>
     </row>
     <row r="435" spans="1:6">
@@ -10400,16 +10403,16 @@
         <v>0.1</v>
       </c>
       <c r="C435">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="D435">
-        <v>858.50577127</v>
+        <v>862.27345843</v>
       </c>
       <c r="E435">
         <v>785.21813144</v>
       </c>
       <c r="F435">
-        <v>73.28763982999999</v>
+        <v>77.05532699000003</v>
       </c>
     </row>
     <row r="436" spans="1:6">
@@ -10420,16 +10423,16 @@
         <v>0.1</v>
       </c>
       <c r="C436">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D436">
-        <v>854.68320816</v>
+        <v>858.50577127</v>
       </c>
       <c r="E436">
         <v>785.21813144</v>
       </c>
       <c r="F436">
-        <v>69.46507672000007</v>
+        <v>73.28763982999999</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -10440,16 +10443,16 @@
         <v>0.1</v>
       </c>
       <c r="C437">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D437">
-        <v>850.80540383</v>
+        <v>854.68320816</v>
       </c>
       <c r="E437">
         <v>785.21813144</v>
       </c>
       <c r="F437">
-        <v>65.58727239000007</v>
+        <v>69.46507672000007</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -10460,16 +10463,16 @@
         <v>0.1</v>
       </c>
       <c r="C438">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D438">
-        <v>846.87203903</v>
+        <v>850.80540383</v>
       </c>
       <c r="E438">
         <v>785.21813144</v>
       </c>
       <c r="F438">
-        <v>61.65390759000002</v>
+        <v>65.58727239000007</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -10480,16 +10483,16 @@
         <v>0.1</v>
       </c>
       <c r="C439">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D439">
-        <v>842.8828412399999</v>
+        <v>846.87203903</v>
       </c>
       <c r="E439">
         <v>785.21813144</v>
       </c>
       <c r="F439">
-        <v>57.66470979999997</v>
+        <v>61.65390759000002</v>
       </c>
     </row>
     <row r="440" spans="1:6">
@@ -10500,16 +10503,16 @@
         <v>0.1</v>
       </c>
       <c r="C440">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="D440">
-        <v>838.83758398</v>
+        <v>842.8828412399999</v>
       </c>
       <c r="E440">
         <v>785.21813144</v>
       </c>
       <c r="F440">
-        <v>53.61945254</v>
+        <v>57.66470979999997</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -10520,15 +10523,35 @@
         <v>0.1</v>
       </c>
       <c r="C441">
+        <v>0.095</v>
+      </c>
+      <c r="D441">
+        <v>838.83758398</v>
+      </c>
+      <c r="E441">
+        <v>785.21813144</v>
+      </c>
+      <c r="F441">
+        <v>53.61945254</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
+      <c r="A442" t="s">
+        <v>446</v>
+      </c>
+      <c r="B442">
         <v>0.1</v>
       </c>
-      <c r="D441">
+      <c r="C442">
+        <v>0.1</v>
+      </c>
+      <c r="D442">
         <v>834.7360867</v>
       </c>
-      <c r="E441">
-        <v>785.21813144</v>
-      </c>
-      <c r="F441">
+      <c r="E442">
+        <v>785.21813144</v>
+      </c>
+      <c r="F442">
         <v>49.51795526000001</v>
       </c>
     </row>
